--- a/_DOCS/Gantt/GanttRéel.xlsx
+++ b/_DOCS/Gantt/GanttRéel.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16DAFC50-DA36-B84A-B485-8DC1E12B5E98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{411020A6-8282-B148-BAE1-187F12B18738}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-4500" yWindow="-21600" windowWidth="38400" windowHeight="21600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="159">
   <si>
     <t>Créez un planning de projet dans cette feuille de calcul.
 Entrez le titre de ce projet dans la cellule B1. 
@@ -325,25 +325,13 @@
     <t>Identification des "Algorithmes Complexes"</t>
   </si>
   <si>
-    <t>Analyse des choix d'implémentation</t>
-  </si>
-  <si>
     <t>Rédaction du journal de bord des difficultés</t>
-  </si>
-  <si>
-    <t>Synthèse des "Fiertés"</t>
-  </si>
-  <si>
-    <t>Bilan de la partie "Système d'Information"</t>
   </si>
   <si>
     <t>Mise à jour finale du Gantt "Réel"</t>
   </si>
   <si>
     <t>Analyse des écarts de planning</t>
-  </si>
-  <si>
-    <t>Répartition des tâches finale</t>
   </si>
   <si>
     <t>Création du diagramme de Gantt "Prévisionnel"</t>
@@ -359,9 +347,6 @@
   </si>
   <si>
     <t>Scénarisation de la démonstration</t>
-  </si>
-  <si>
-    <t>Préparation aux questions-réponses</t>
   </si>
   <si>
     <t>DEV</t>
@@ -576,6 +561,15 @@
   <si>
     <t>??</t>
   </si>
+  <si>
+    <t>Création de pièces personnalisées</t>
+  </si>
+  <si>
+    <t>e</t>
+  </si>
+  <si>
+    <t>Implémentation des pièces personnalisées</t>
+  </si>
 </sst>
 </file>
 
@@ -590,9 +584,16 @@
     <numFmt numFmtId="169" formatCode="d/m/yy;@"/>
     <numFmt numFmtId="170" formatCode="d"/>
   </numFmts>
-  <fonts count="44">
+  <fonts count="45">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -1472,76 +1473,76 @@
   </borders>
   <cellStyleXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="9" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
-    <xf numFmtId="167" fontId="17" fillId="0" borderId="3" applyFont="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyProtection="0">
+    <xf numFmtId="9" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
+    <xf numFmtId="167" fontId="18" fillId="0" borderId="3" applyFont="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyProtection="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyProtection="0">
       <alignment horizontal="right" indent="1"/>
     </xf>
-    <xf numFmtId="168" fontId="17" fillId="0" borderId="3">
+    <xf numFmtId="168" fontId="18" fillId="0" borderId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="17" fillId="0" borderId="2" applyFill="0">
+    <xf numFmtId="169" fontId="18" fillId="0" borderId="2" applyFill="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyFill="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyFill="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyFill="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyFill="0">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="27" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="29" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="30" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="31" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="32" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="34" fillId="13" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="11" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="28" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="30" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="31" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="32" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="33" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="35" fillId="13" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="11" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="118">
+  <cellXfs count="122">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1555,27 +1556,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="9" fontId="14" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="13" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="14" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1584,65 +1585,65 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="3"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="3"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="5" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="5" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="11">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="11">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="12">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="12">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="169" fontId="17" fillId="0" borderId="2" xfId="10">
+    <xf numFmtId="169" fontId="18" fillId="0" borderId="2" xfId="10">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="12" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="13" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="13" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="14" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="39" fillId="3" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="40" fillId="3" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="3" borderId="2" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="40" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="40" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="40" fillId="39" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="9" fillId="3" borderId="2" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="39" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="39" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="39" fillId="39" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="3" borderId="2" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1651,10 +1652,10 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="39" fillId="40" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="40" fillId="40" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="40" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="40" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="40" borderId="0" xfId="0" applyFill="1"/>
@@ -1662,7 +1663,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="40" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1674,14 +1675,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyProtection="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="41" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="41" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1691,109 +1692,109 @@
     <xf numFmtId="0" fontId="0" fillId="41" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="11" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="11" applyFont="1" applyFill="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="39" fillId="5" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="40" fillId="5" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="39" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="40" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="7" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="7" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="12" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="12" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="4"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="12" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="12" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="4"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="11" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="11" applyFont="1" applyFill="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="43" borderId="2" xfId="12" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="39" fillId="43" borderId="2" xfId="12" applyFont="1" applyFill="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="43" borderId="2" xfId="11" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="43" borderId="2" xfId="11" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="39" fillId="43" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="40" fillId="43" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="9" fillId="43" borderId="2" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1">
+    <xf numFmtId="14" fontId="10" fillId="43" borderId="2" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="44" borderId="2" xfId="12" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="44" borderId="2" xfId="12" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="44" borderId="2" xfId="11" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="44" borderId="2" xfId="11" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="39" fillId="44" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="40" fillId="44" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="9" fillId="44" borderId="2" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1">
+    <xf numFmtId="14" fontId="10" fillId="44" borderId="2" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="39" borderId="2" xfId="12" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="39" borderId="2" xfId="12" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="7"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="39" borderId="2" xfId="11" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="39" borderId="2" xfId="11" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="9" fillId="39" borderId="2" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1">
+    <xf numFmtId="14" fontId="10" fillId="39" borderId="2" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="42" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="44" fillId="42" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="42" borderId="2" xfId="11" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="42" borderId="2" xfId="11" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="37" fillId="42" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="38" fillId="42" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="37" fillId="42" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="44" borderId="2" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1">
+    <xf numFmtId="14" fontId="38" fillId="42" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="3" fillId="44" borderId="2" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="4" fillId="44" borderId="2" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="39" borderId="2" xfId="11" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="39" borderId="2" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="45" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="45" borderId="2" xfId="11" applyFont="1" applyFill="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="38" fillId="45" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="38" fillId="45" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="11" applyFont="1" applyFill="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="12" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="4"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="39" borderId="2" xfId="11" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="39" borderId="2" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="45" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="45" borderId="2" xfId="11" applyFont="1" applyFill="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="37" fillId="45" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="37" fillId="45" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="11" applyFont="1" applyFill="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="12" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="4"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="39" borderId="2" xfId="11" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="39" borderId="2" xfId="12" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="39" borderId="2" xfId="12" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="7"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="39" borderId="2" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1">
+    <xf numFmtId="14" fontId="2" fillId="39" borderId="2" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1805,10 +1806,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="41" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1820,53 +1821,65 @@
     <xf numFmtId="0" fontId="0" fillId="41" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="40" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="9" fillId="40" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="17" fillId="0" borderId="24" xfId="9" applyNumberFormat="1" applyBorder="1">
+    <xf numFmtId="49" fontId="10" fillId="40" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="18" fillId="0" borderId="24" xfId="9" applyNumberFormat="1" applyBorder="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="17" fillId="0" borderId="25" xfId="9" applyNumberFormat="1" applyBorder="1">
+    <xf numFmtId="14" fontId="18" fillId="0" borderId="25" xfId="9" applyNumberFormat="1" applyBorder="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="8">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="8">
       <alignment horizontal="right" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="8" applyBorder="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="8" applyBorder="1">
       <alignment horizontal="right" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="8" applyFill="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="8" applyFill="1">
       <alignment horizontal="right" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="8" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="8" applyFill="1" applyBorder="1">
       <alignment horizontal="right" indent="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="5" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="5" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="5" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="5" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="5" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="5" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="5" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="5" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="39" borderId="2" xfId="12" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="7"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="39" borderId="2" xfId="11" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="11" applyFont="1" applyFill="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="3" borderId="2" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="54">
@@ -2488,7 +2501,7 @@
   <sheetPr codeName="Sheet1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:GK110"/>
+  <dimension ref="A1:GK107"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="30" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="16" customWidth="1"/>
@@ -3899,12 +3912,12 @@
       </c>
       <c r="F9" s="80">
         <f>MAX(F10,F21,F32)</f>
-        <v>46183</v>
+        <v>46187</v>
       </c>
       <c r="G9" s="9"/>
       <c r="H9" s="9">
-        <f t="shared" ref="H9:H107" si="71">IF(OR(ISBLANK(début_tâche),ISBLANK(fin_tâche)),"",fin_tâche-début_tâche+1)</f>
-        <v>129</v>
+        <f t="shared" ref="H9:H104" si="71">IF(OR(ISBLANK(début_tâche),ISBLANK(fin_tâche)),"",fin_tâche-début_tâche+1)</f>
+        <v>133</v>
       </c>
       <c r="I9" s="94"/>
       <c r="J9" s="95"/>
@@ -4097,7 +4110,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="66" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C10" s="67" t="s">
         <v>57</v>
@@ -4477,7 +4490,7 @@
       <c r="EV11" s="95"/>
       <c r="EW11" s="96"/>
       <c r="EX11" s="44">
-        <f t="shared" ref="EX11:EX49" si="72">IF(OR(F11 = "?",E11 = "?"), 0, F11-E11)</f>
+        <f t="shared" ref="EX11:EX44" si="72">IF(OR(F11 = "?",E11 = "?"), 0, F11-E11)</f>
         <v>2</v>
       </c>
       <c r="EY11" s="44"/>
@@ -4526,7 +4539,7 @@
         <v>60</v>
       </c>
       <c r="C12" s="65" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D12" s="30">
         <v>1</v>
@@ -4731,7 +4744,7 @@
         <v>62</v>
       </c>
       <c r="C13" s="65" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="D13" s="30">
         <v>1</v>
@@ -4936,7 +4949,7 @@
         <v>61</v>
       </c>
       <c r="C14" s="65" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D14" s="30">
         <v>1</v>
@@ -5138,7 +5151,7 @@
     <row r="15" spans="1:193" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A15" s="17"/>
       <c r="B15" s="63" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="C15" s="65" t="s">
         <v>57</v>
@@ -5958,7 +5971,7 @@
     <row r="19" spans="1:193" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A19" s="17"/>
       <c r="B19" s="64" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C19" s="65" t="s">
         <v>26</v>
@@ -6373,7 +6386,7 @@
         <v>8</v>
       </c>
       <c r="B21" s="66" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="C21" s="67" t="s">
         <v>57</v>
@@ -6591,7 +6604,7 @@
         <v>65</v>
       </c>
       <c r="C22" s="89" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="D22" s="30">
         <v>1</v>
@@ -6802,7 +6815,7 @@
         <v>66</v>
       </c>
       <c r="C23" s="89" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="D23" s="30">
         <v>1</v>
@@ -7007,7 +7020,7 @@
         <v>67</v>
       </c>
       <c r="C24" s="89" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="D24" s="30">
         <v>1</v>
@@ -7212,7 +7225,7 @@
         <v>68</v>
       </c>
       <c r="C25" s="89" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="D25" s="30">
         <v>1</v>
@@ -7417,7 +7430,7 @@
         <v>69</v>
       </c>
       <c r="C26" s="89" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="D26" s="30">
         <v>1</v>
@@ -7622,7 +7635,7 @@
         <v>70</v>
       </c>
       <c r="C27" s="89" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="D27" s="30">
         <v>1</v>
@@ -7827,7 +7840,7 @@
         <v>71</v>
       </c>
       <c r="C28" s="89" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="D28" s="30">
         <v>1</v>
@@ -8234,10 +8247,10 @@
     <row r="30" spans="1:193" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A30" s="17"/>
       <c r="B30" s="90" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C30" s="89" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D30" s="30">
         <v>1</v>
@@ -8646,26 +8659,26 @@
         <v>8</v>
       </c>
       <c r="B32" s="66" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C32" s="67" t="s">
         <v>57</v>
       </c>
       <c r="D32" s="68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E32" s="69">
-        <f>MIN(E33:E46)</f>
-        <v>46146</v>
+        <f>MIN(E33:E41)</f>
+        <v>46160</v>
       </c>
       <c r="F32" s="69">
-        <f>MAX(F33:F46)</f>
-        <v>46183</v>
+        <f>MAX(F33:F41)</f>
+        <v>46187</v>
       </c>
       <c r="G32" s="9"/>
       <c r="H32" s="9">
         <f t="shared" si="71"/>
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="I32" s="94"/>
       <c r="J32" s="95"/>
@@ -8814,7 +8827,7 @@
       <c r="EW32" s="96"/>
       <c r="EX32" s="44">
         <f>IF(OR(F32 = "?",E32 = "?"), 0, F32-E32)</f>
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="EY32" s="44"/>
       <c r="EZ32" s="44"/>
@@ -8864,16 +8877,16 @@
         <v>75</v>
       </c>
       <c r="C33" s="59" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D33" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E33" s="38">
-        <v>46146</v>
+        <v>46186</v>
       </c>
       <c r="F33" s="31">
-        <v>46147</v>
+        <v>46187</v>
       </c>
       <c r="G33" s="9"/>
       <c r="H33" s="9">
@@ -9074,17 +9087,17 @@
       <c r="B34" s="63" t="s">
         <v>76</v>
       </c>
-      <c r="C34" s="59" t="s">
-        <v>143</v>
+      <c r="C34" s="120" t="s">
+        <v>139</v>
       </c>
       <c r="D34" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E34" s="38">
-        <v>46150</v>
+        <v>46186</v>
       </c>
       <c r="F34" s="31">
-        <v>46150</v>
+        <v>46187</v>
       </c>
       <c r="G34" s="9"/>
       <c r="H34" s="9"/>
@@ -9279,17 +9292,17 @@
       <c r="B35" s="63" t="s">
         <v>77</v>
       </c>
-      <c r="C35" s="59" t="s">
-        <v>143</v>
+      <c r="C35" s="120" t="s">
+        <v>26</v>
       </c>
       <c r="D35" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E35" s="38">
         <v>46160</v>
       </c>
       <c r="F35" s="31">
-        <v>46161</v>
+        <v>46187</v>
       </c>
       <c r="G35" s="9"/>
       <c r="H35" s="9"/>
@@ -9488,13 +9501,13 @@
         <v>26</v>
       </c>
       <c r="D36" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E36" s="38">
-        <v>46160</v>
+        <v>46183</v>
       </c>
       <c r="F36" s="31">
-        <v>46161</v>
+        <v>46187</v>
       </c>
       <c r="G36" s="9"/>
       <c r="H36" s="9"/>
@@ -9693,13 +9706,13 @@
         <v>26</v>
       </c>
       <c r="D37" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E37" s="38">
-        <v>46162</v>
+        <v>46186</v>
       </c>
       <c r="F37" s="31">
-        <v>46163</v>
+        <v>46187</v>
       </c>
       <c r="G37" s="9"/>
       <c r="H37" s="9"/>
@@ -9892,19 +9905,19 @@
     <row r="38" spans="1:193" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A38" s="17"/>
       <c r="B38" s="63" t="s">
-        <v>80</v>
-      </c>
-      <c r="C38" s="59" t="s">
-        <v>143</v>
+        <v>82</v>
+      </c>
+      <c r="C38" s="120" t="s">
+        <v>57</v>
       </c>
       <c r="D38" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E38" s="38">
-        <v>46162</v>
+        <v>46187</v>
       </c>
       <c r="F38" s="31">
-        <v>46163</v>
+        <v>46187</v>
       </c>
       <c r="G38" s="9"/>
       <c r="H38" s="9"/>
@@ -10097,19 +10110,19 @@
     <row r="39" spans="1:193" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A39" s="17"/>
       <c r="B39" s="63" t="s">
-        <v>81</v>
-      </c>
-      <c r="C39" s="59" t="s">
-        <v>26</v>
+        <v>83</v>
+      </c>
+      <c r="C39" s="120" t="s">
+        <v>57</v>
       </c>
       <c r="D39" s="30">
         <v>0.5</v>
       </c>
       <c r="E39" s="38">
-        <v>46183</v>
-      </c>
-      <c r="F39" s="31">
-        <v>46183</v>
+        <v>46174</v>
+      </c>
+      <c r="F39" s="121" t="s">
+        <v>155</v>
       </c>
       <c r="G39" s="9"/>
       <c r="H39" s="9"/>
@@ -10302,19 +10315,19 @@
     <row r="40" spans="1:193" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A40" s="17"/>
       <c r="B40" s="63" t="s">
-        <v>82</v>
-      </c>
-      <c r="C40" s="59" t="s">
-        <v>26</v>
+        <v>84</v>
+      </c>
+      <c r="C40" s="120" t="s">
+        <v>138</v>
       </c>
       <c r="D40" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E40" s="38">
-        <v>46175</v>
+        <v>46186</v>
       </c>
       <c r="F40" s="31">
-        <v>46176</v>
+        <v>46187</v>
       </c>
       <c r="G40" s="9"/>
       <c r="H40" s="9"/>
@@ -10507,19 +10520,19 @@
     <row r="41" spans="1:193" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A41" s="17"/>
       <c r="B41" s="63" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C41" s="59" t="s">
-        <v>143</v>
+        <v>57</v>
       </c>
       <c r="D41" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E41" s="38">
-        <v>46177</v>
+        <v>46174</v>
       </c>
       <c r="F41" s="31">
-        <v>46178</v>
+        <v>46187</v>
       </c>
       <c r="G41" s="9"/>
       <c r="H41" s="9"/>
@@ -10710,170 +10723,181 @@
       <c r="GK41" s="44"/>
     </row>
     <row r="42" spans="1:193" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
-      <c r="A42" s="17"/>
-      <c r="B42" s="63" t="s">
-        <v>86</v>
-      </c>
-      <c r="C42" s="59" t="s">
-        <v>144</v>
-      </c>
-      <c r="D42" s="30">
-        <v>0</v>
-      </c>
-      <c r="E42" s="38">
-        <v>46174</v>
-      </c>
-      <c r="F42" s="31">
-        <v>46174</v>
+      <c r="A42" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="B42" s="85" t="s">
+        <v>85</v>
+      </c>
+      <c r="C42" s="86" t="s">
+        <v>57</v>
+      </c>
+      <c r="D42" s="87">
+        <f>SUMPRODUCT(D43:D102,EX43:EX102) / SUM(EX43:EX102)</f>
+        <v>1</v>
+      </c>
+      <c r="E42" s="88">
+        <f>MIN(E43,E57,E67,E76,E86)</f>
+        <v>46097</v>
+      </c>
+      <c r="F42" s="88">
+        <f>MAX(F43,F57,F67,F86,F76)</f>
+        <v>46183</v>
       </c>
       <c r="G42" s="9"/>
-      <c r="H42" s="9"/>
-      <c r="I42" s="47"/>
-      <c r="J42" s="48"/>
-      <c r="K42" s="48"/>
-      <c r="L42" s="48"/>
-      <c r="M42" s="49"/>
+      <c r="H42" s="9">
+        <f t="shared" si="71"/>
+        <v>87</v>
+      </c>
+      <c r="I42" s="94"/>
+      <c r="J42" s="95"/>
+      <c r="K42" s="95"/>
+      <c r="L42" s="95"/>
+      <c r="M42" s="96"/>
       <c r="N42" s="39"/>
       <c r="O42" s="39"/>
-      <c r="P42" s="56"/>
-      <c r="Q42" s="57"/>
-      <c r="R42" s="57"/>
-      <c r="S42" s="57"/>
-      <c r="T42" s="58"/>
-      <c r="U42" s="40"/>
-      <c r="V42" s="40"/>
-      <c r="W42" s="47"/>
-      <c r="X42" s="48"/>
-      <c r="Y42" s="48"/>
-      <c r="Z42" s="48"/>
-      <c r="AA42" s="49"/>
+      <c r="P42" s="99"/>
+      <c r="Q42" s="100"/>
+      <c r="R42" s="100"/>
+      <c r="S42" s="100"/>
+      <c r="T42" s="101"/>
+      <c r="U42" s="39"/>
+      <c r="V42" s="39"/>
+      <c r="W42" s="94"/>
+      <c r="X42" s="95"/>
+      <c r="Y42" s="95"/>
+      <c r="Z42" s="95"/>
+      <c r="AA42" s="96"/>
       <c r="AB42" s="39"/>
       <c r="AC42" s="39"/>
-      <c r="AD42" s="56"/>
-      <c r="AE42" s="57"/>
-      <c r="AF42" s="57"/>
-      <c r="AG42" s="57"/>
-      <c r="AH42" s="58"/>
+      <c r="AD42" s="99"/>
+      <c r="AE42" s="100"/>
+      <c r="AF42" s="100"/>
+      <c r="AG42" s="100"/>
+      <c r="AH42" s="101"/>
       <c r="AI42" s="39"/>
       <c r="AJ42" s="39"/>
-      <c r="AK42" s="47"/>
-      <c r="AL42" s="48"/>
-      <c r="AM42" s="48"/>
-      <c r="AN42" s="48"/>
-      <c r="AO42" s="49"/>
+      <c r="AK42" s="94"/>
+      <c r="AL42" s="95"/>
+      <c r="AM42" s="95"/>
+      <c r="AN42" s="95"/>
+      <c r="AO42" s="96"/>
       <c r="AP42" s="39"/>
       <c r="AQ42" s="39"/>
-      <c r="AR42" s="56"/>
-      <c r="AS42" s="57"/>
-      <c r="AT42" s="57"/>
-      <c r="AU42" s="57"/>
-      <c r="AV42" s="58"/>
+      <c r="AR42" s="99"/>
+      <c r="AS42" s="100"/>
+      <c r="AT42" s="100"/>
+      <c r="AU42" s="100"/>
+      <c r="AV42" s="101"/>
       <c r="AW42" s="39"/>
       <c r="AX42" s="39"/>
-      <c r="AY42" s="47"/>
-      <c r="AZ42" s="48"/>
-      <c r="BA42" s="48"/>
-      <c r="BB42" s="48"/>
-      <c r="BC42" s="49"/>
+      <c r="AY42" s="94"/>
+      <c r="AZ42" s="95"/>
+      <c r="BA42" s="95"/>
+      <c r="BB42" s="95"/>
+      <c r="BC42" s="96"/>
       <c r="BD42" s="39"/>
       <c r="BE42" s="39"/>
-      <c r="BF42" s="56"/>
-      <c r="BG42" s="57"/>
-      <c r="BH42" s="57"/>
-      <c r="BI42" s="57"/>
-      <c r="BJ42" s="58"/>
+      <c r="BF42" s="99"/>
+      <c r="BG42" s="100"/>
+      <c r="BH42" s="100"/>
+      <c r="BI42" s="100"/>
+      <c r="BJ42" s="101"/>
       <c r="BK42" s="39"/>
       <c r="BL42" s="39"/>
-      <c r="BM42" s="47"/>
-      <c r="BN42" s="48"/>
-      <c r="BO42" s="48"/>
-      <c r="BP42" s="48"/>
-      <c r="BQ42" s="49"/>
+      <c r="BM42" s="94"/>
+      <c r="BN42" s="95"/>
+      <c r="BO42" s="95"/>
+      <c r="BP42" s="95"/>
+      <c r="BQ42" s="96"/>
       <c r="BR42" s="39"/>
       <c r="BS42" s="39"/>
-      <c r="BT42" s="47"/>
-      <c r="BU42" s="48"/>
-      <c r="BV42" s="48"/>
-      <c r="BW42" s="48"/>
-      <c r="BX42" s="49"/>
+      <c r="BT42" s="94"/>
+      <c r="BU42" s="95"/>
+      <c r="BV42" s="95"/>
+      <c r="BW42" s="95"/>
+      <c r="BX42" s="96"/>
       <c r="BY42" s="39"/>
       <c r="BZ42" s="39"/>
-      <c r="CA42" s="56"/>
-      <c r="CB42" s="57"/>
-      <c r="CC42" s="57"/>
-      <c r="CD42" s="57"/>
-      <c r="CE42" s="58"/>
+      <c r="CA42" s="99"/>
+      <c r="CB42" s="100"/>
+      <c r="CC42" s="100"/>
+      <c r="CD42" s="100"/>
+      <c r="CE42" s="101"/>
       <c r="CF42" s="39"/>
       <c r="CG42" s="39"/>
-      <c r="CH42" s="47"/>
-      <c r="CI42" s="48"/>
-      <c r="CJ42" s="48"/>
-      <c r="CK42" s="48"/>
-      <c r="CL42" s="49"/>
+      <c r="CH42" s="94"/>
+      <c r="CI42" s="95"/>
+      <c r="CJ42" s="95"/>
+      <c r="CK42" s="95"/>
+      <c r="CL42" s="96"/>
       <c r="CM42" s="39"/>
       <c r="CN42" s="39"/>
-      <c r="CO42" s="56"/>
-      <c r="CP42" s="57"/>
-      <c r="CQ42" s="57"/>
-      <c r="CR42" s="57"/>
-      <c r="CS42" s="58"/>
+      <c r="CO42" s="99"/>
+      <c r="CP42" s="100"/>
+      <c r="CQ42" s="100"/>
+      <c r="CR42" s="100"/>
+      <c r="CS42" s="101"/>
       <c r="CT42" s="39"/>
       <c r="CU42" s="39"/>
-      <c r="CV42" s="47"/>
-      <c r="CW42" s="48"/>
-      <c r="CX42" s="48"/>
-      <c r="CY42" s="48"/>
-      <c r="CZ42" s="49"/>
+      <c r="CV42" s="94"/>
+      <c r="CW42" s="95"/>
+      <c r="CX42" s="95"/>
+      <c r="CY42" s="95"/>
+      <c r="CZ42" s="96"/>
       <c r="DA42" s="39"/>
       <c r="DB42" s="39"/>
-      <c r="DC42" s="56"/>
-      <c r="DD42" s="57"/>
-      <c r="DE42" s="57"/>
-      <c r="DF42" s="57"/>
-      <c r="DG42" s="58"/>
+      <c r="DC42" s="99"/>
+      <c r="DD42" s="100"/>
+      <c r="DE42" s="100"/>
+      <c r="DF42" s="100"/>
+      <c r="DG42" s="101"/>
       <c r="DH42" s="39"/>
       <c r="DI42" s="39"/>
-      <c r="DJ42" s="47"/>
-      <c r="DK42" s="48"/>
-      <c r="DL42" s="48"/>
-      <c r="DM42" s="48"/>
-      <c r="DN42" s="49"/>
+      <c r="DJ42" s="94"/>
+      <c r="DK42" s="95"/>
+      <c r="DL42" s="95"/>
+      <c r="DM42" s="95"/>
+      <c r="DN42" s="96"/>
       <c r="DO42" s="39"/>
       <c r="DP42" s="39"/>
-      <c r="DQ42" s="56"/>
-      <c r="DR42" s="57"/>
-      <c r="DS42" s="57"/>
-      <c r="DT42" s="57"/>
-      <c r="DU42" s="58"/>
+      <c r="DQ42" s="99"/>
+      <c r="DR42" s="100"/>
+      <c r="DS42" s="100"/>
+      <c r="DT42" s="100"/>
+      <c r="DU42" s="101"/>
       <c r="DV42" s="39"/>
       <c r="DW42" s="39"/>
-      <c r="DX42" s="47"/>
-      <c r="DY42" s="48"/>
-      <c r="DZ42" s="48"/>
-      <c r="EA42" s="48"/>
-      <c r="EB42" s="49"/>
+      <c r="DX42" s="94"/>
+      <c r="DY42" s="95"/>
+      <c r="DZ42" s="95"/>
+      <c r="EA42" s="95"/>
+      <c r="EB42" s="96"/>
       <c r="EC42" s="39"/>
       <c r="ED42" s="39"/>
-      <c r="EE42" s="56"/>
-      <c r="EF42" s="57"/>
-      <c r="EG42" s="57"/>
-      <c r="EH42" s="57"/>
-      <c r="EI42" s="58"/>
+      <c r="EE42" s="99"/>
+      <c r="EF42" s="100"/>
+      <c r="EG42" s="100"/>
+      <c r="EH42" s="100"/>
+      <c r="EI42" s="101"/>
       <c r="EJ42" s="39"/>
       <c r="EK42" s="39"/>
-      <c r="EL42" s="47"/>
-      <c r="EM42" s="48"/>
-      <c r="EN42" s="48"/>
-      <c r="EO42" s="48"/>
-      <c r="EP42" s="49"/>
+      <c r="EL42" s="94"/>
+      <c r="EM42" s="95"/>
+      <c r="EN42" s="95"/>
+      <c r="EO42" s="95"/>
+      <c r="EP42" s="96"/>
       <c r="EQ42" s="39"/>
       <c r="ER42" s="39"/>
-      <c r="ES42" s="47"/>
-      <c r="ET42" s="48"/>
-      <c r="EU42" s="48"/>
-      <c r="EV42" s="48"/>
-      <c r="EW42" s="49"/>
-      <c r="EX42" s="44"/>
+      <c r="ES42" s="94"/>
+      <c r="ET42" s="95"/>
+      <c r="EU42" s="95"/>
+      <c r="EV42" s="95"/>
+      <c r="EW42" s="96"/>
+      <c r="EX42" s="44">
+        <f t="shared" si="72"/>
+        <v>86</v>
+      </c>
       <c r="EY42" s="44"/>
       <c r="EZ42" s="44"/>
       <c r="FA42" s="44"/>
@@ -10916,169 +10940,177 @@
     </row>
     <row r="43" spans="1:193" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A43" s="17"/>
-      <c r="B43" s="63" t="s">
-        <v>87</v>
-      </c>
-      <c r="C43" s="59" t="s">
-        <v>26</v>
-      </c>
-      <c r="D43" s="30">
-        <v>0</v>
-      </c>
-      <c r="E43" s="38">
-        <v>46177</v>
-      </c>
-      <c r="F43" s="31">
-        <v>46178</v>
+      <c r="B43" s="70" t="s">
+        <v>153</v>
+      </c>
+      <c r="C43" s="71" t="s">
+        <v>57</v>
+      </c>
+      <c r="D43" s="72">
+        <v>1</v>
+      </c>
+      <c r="E43" s="81">
+        <f>MIN(E44:E56)</f>
+        <v>46097</v>
+      </c>
+      <c r="F43" s="82">
+        <f>MAX(F44:F56)</f>
+        <v>46174</v>
       </c>
       <c r="G43" s="9"/>
-      <c r="H43" s="9"/>
-      <c r="I43" s="47"/>
-      <c r="J43" s="48"/>
-      <c r="K43" s="48"/>
-      <c r="L43" s="48"/>
-      <c r="M43" s="49"/>
+      <c r="H43" s="9">
+        <f t="shared" si="71"/>
+        <v>78</v>
+      </c>
+      <c r="I43" s="94"/>
+      <c r="J43" s="95"/>
+      <c r="K43" s="95"/>
+      <c r="L43" s="95"/>
+      <c r="M43" s="96"/>
       <c r="N43" s="39"/>
       <c r="O43" s="39"/>
-      <c r="P43" s="56"/>
-      <c r="Q43" s="57"/>
-      <c r="R43" s="57"/>
-      <c r="S43" s="57"/>
-      <c r="T43" s="58"/>
-      <c r="U43" s="40"/>
-      <c r="V43" s="40"/>
-      <c r="W43" s="47"/>
-      <c r="X43" s="48"/>
-      <c r="Y43" s="48"/>
-      <c r="Z43" s="48"/>
-      <c r="AA43" s="49"/>
+      <c r="P43" s="99"/>
+      <c r="Q43" s="100"/>
+      <c r="R43" s="100"/>
+      <c r="S43" s="100"/>
+      <c r="T43" s="101"/>
+      <c r="U43" s="39"/>
+      <c r="V43" s="39"/>
+      <c r="W43" s="94"/>
+      <c r="X43" s="95"/>
+      <c r="Y43" s="95"/>
+      <c r="Z43" s="95"/>
+      <c r="AA43" s="96"/>
       <c r="AB43" s="39"/>
       <c r="AC43" s="39"/>
-      <c r="AD43" s="56"/>
-      <c r="AE43" s="57"/>
-      <c r="AF43" s="57"/>
-      <c r="AG43" s="57"/>
-      <c r="AH43" s="58"/>
+      <c r="AD43" s="99"/>
+      <c r="AE43" s="100"/>
+      <c r="AF43" s="100"/>
+      <c r="AG43" s="100"/>
+      <c r="AH43" s="101"/>
       <c r="AI43" s="39"/>
       <c r="AJ43" s="39"/>
-      <c r="AK43" s="47"/>
-      <c r="AL43" s="48"/>
-      <c r="AM43" s="48"/>
-      <c r="AN43" s="48"/>
-      <c r="AO43" s="49"/>
+      <c r="AK43" s="94"/>
+      <c r="AL43" s="95"/>
+      <c r="AM43" s="95"/>
+      <c r="AN43" s="95"/>
+      <c r="AO43" s="96"/>
       <c r="AP43" s="39"/>
       <c r="AQ43" s="39"/>
-      <c r="AR43" s="56"/>
-      <c r="AS43" s="57"/>
-      <c r="AT43" s="57"/>
-      <c r="AU43" s="57"/>
-      <c r="AV43" s="58"/>
+      <c r="AR43" s="99"/>
+      <c r="AS43" s="100"/>
+      <c r="AT43" s="100"/>
+      <c r="AU43" s="100"/>
+      <c r="AV43" s="101"/>
       <c r="AW43" s="39"/>
       <c r="AX43" s="39"/>
-      <c r="AY43" s="47"/>
-      <c r="AZ43" s="48"/>
-      <c r="BA43" s="48"/>
-      <c r="BB43" s="48"/>
-      <c r="BC43" s="49"/>
+      <c r="AY43" s="94"/>
+      <c r="AZ43" s="95"/>
+      <c r="BA43" s="95"/>
+      <c r="BB43" s="95"/>
+      <c r="BC43" s="96"/>
       <c r="BD43" s="39"/>
       <c r="BE43" s="39"/>
-      <c r="BF43" s="56"/>
-      <c r="BG43" s="57"/>
-      <c r="BH43" s="57"/>
-      <c r="BI43" s="57"/>
-      <c r="BJ43" s="58"/>
+      <c r="BF43" s="99"/>
+      <c r="BG43" s="100"/>
+      <c r="BH43" s="100"/>
+      <c r="BI43" s="100"/>
+      <c r="BJ43" s="101"/>
       <c r="BK43" s="39"/>
       <c r="BL43" s="39"/>
-      <c r="BM43" s="47"/>
-      <c r="BN43" s="48"/>
-      <c r="BO43" s="48"/>
-      <c r="BP43" s="48"/>
-      <c r="BQ43" s="49"/>
+      <c r="BM43" s="94"/>
+      <c r="BN43" s="95"/>
+      <c r="BO43" s="95"/>
+      <c r="BP43" s="95"/>
+      <c r="BQ43" s="96"/>
       <c r="BR43" s="39"/>
       <c r="BS43" s="39"/>
-      <c r="BT43" s="47"/>
-      <c r="BU43" s="48"/>
-      <c r="BV43" s="48"/>
-      <c r="BW43" s="48"/>
-      <c r="BX43" s="49"/>
+      <c r="BT43" s="94"/>
+      <c r="BU43" s="95"/>
+      <c r="BV43" s="95"/>
+      <c r="BW43" s="95"/>
+      <c r="BX43" s="96"/>
       <c r="BY43" s="39"/>
       <c r="BZ43" s="39"/>
-      <c r="CA43" s="56"/>
-      <c r="CB43" s="57"/>
-      <c r="CC43" s="57"/>
-      <c r="CD43" s="57"/>
-      <c r="CE43" s="58"/>
+      <c r="CA43" s="99"/>
+      <c r="CB43" s="100"/>
+      <c r="CC43" s="100"/>
+      <c r="CD43" s="100"/>
+      <c r="CE43" s="101"/>
       <c r="CF43" s="39"/>
       <c r="CG43" s="39"/>
-      <c r="CH43" s="47"/>
-      <c r="CI43" s="48"/>
-      <c r="CJ43" s="48"/>
-      <c r="CK43" s="48"/>
-      <c r="CL43" s="49"/>
+      <c r="CH43" s="94"/>
+      <c r="CI43" s="95"/>
+      <c r="CJ43" s="95"/>
+      <c r="CK43" s="95"/>
+      <c r="CL43" s="96"/>
       <c r="CM43" s="39"/>
       <c r="CN43" s="39"/>
-      <c r="CO43" s="56"/>
-      <c r="CP43" s="57"/>
-      <c r="CQ43" s="57"/>
-      <c r="CR43" s="57"/>
-      <c r="CS43" s="58"/>
+      <c r="CO43" s="99"/>
+      <c r="CP43" s="100"/>
+      <c r="CQ43" s="100"/>
+      <c r="CR43" s="100"/>
+      <c r="CS43" s="101"/>
       <c r="CT43" s="39"/>
       <c r="CU43" s="39"/>
-      <c r="CV43" s="47"/>
-      <c r="CW43" s="48"/>
-      <c r="CX43" s="48"/>
-      <c r="CY43" s="48"/>
-      <c r="CZ43" s="49"/>
+      <c r="CV43" s="94"/>
+      <c r="CW43" s="95"/>
+      <c r="CX43" s="95"/>
+      <c r="CY43" s="95"/>
+      <c r="CZ43" s="96"/>
       <c r="DA43" s="39"/>
       <c r="DB43" s="39"/>
-      <c r="DC43" s="56"/>
-      <c r="DD43" s="57"/>
-      <c r="DE43" s="57"/>
-      <c r="DF43" s="57"/>
-      <c r="DG43" s="58"/>
+      <c r="DC43" s="99"/>
+      <c r="DD43" s="100"/>
+      <c r="DE43" s="100"/>
+      <c r="DF43" s="100"/>
+      <c r="DG43" s="101"/>
       <c r="DH43" s="39"/>
       <c r="DI43" s="39"/>
-      <c r="DJ43" s="47"/>
-      <c r="DK43" s="48"/>
-      <c r="DL43" s="48"/>
-      <c r="DM43" s="48"/>
-      <c r="DN43" s="49"/>
+      <c r="DJ43" s="94"/>
+      <c r="DK43" s="95"/>
+      <c r="DL43" s="95"/>
+      <c r="DM43" s="95"/>
+      <c r="DN43" s="96"/>
       <c r="DO43" s="39"/>
       <c r="DP43" s="39"/>
-      <c r="DQ43" s="56"/>
-      <c r="DR43" s="57"/>
-      <c r="DS43" s="57"/>
-      <c r="DT43" s="57"/>
-      <c r="DU43" s="58"/>
+      <c r="DQ43" s="99"/>
+      <c r="DR43" s="100"/>
+      <c r="DS43" s="100"/>
+      <c r="DT43" s="100"/>
+      <c r="DU43" s="101"/>
       <c r="DV43" s="39"/>
       <c r="DW43" s="39"/>
-      <c r="DX43" s="47"/>
-      <c r="DY43" s="48"/>
-      <c r="DZ43" s="48"/>
-      <c r="EA43" s="48"/>
-      <c r="EB43" s="49"/>
+      <c r="DX43" s="94"/>
+      <c r="DY43" s="95"/>
+      <c r="DZ43" s="95"/>
+      <c r="EA43" s="95"/>
+      <c r="EB43" s="96"/>
       <c r="EC43" s="39"/>
       <c r="ED43" s="39"/>
-      <c r="EE43" s="56"/>
-      <c r="EF43" s="57"/>
-      <c r="EG43" s="57"/>
-      <c r="EH43" s="57"/>
-      <c r="EI43" s="58"/>
+      <c r="EE43" s="99"/>
+      <c r="EF43" s="100"/>
+      <c r="EG43" s="100"/>
+      <c r="EH43" s="100"/>
+      <c r="EI43" s="101"/>
       <c r="EJ43" s="39"/>
       <c r="EK43" s="39"/>
-      <c r="EL43" s="47"/>
-      <c r="EM43" s="48"/>
-      <c r="EN43" s="48"/>
-      <c r="EO43" s="48"/>
-      <c r="EP43" s="49"/>
+      <c r="EL43" s="94"/>
+      <c r="EM43" s="95"/>
+      <c r="EN43" s="95"/>
+      <c r="EO43" s="95"/>
+      <c r="EP43" s="96"/>
       <c r="EQ43" s="39"/>
       <c r="ER43" s="39"/>
-      <c r="ES43" s="47"/>
-      <c r="ET43" s="48"/>
-      <c r="EU43" s="48"/>
-      <c r="EV43" s="48"/>
-      <c r="EW43" s="49"/>
-      <c r="EX43" s="44"/>
+      <c r="ES43" s="94"/>
+      <c r="ET43" s="95"/>
+      <c r="EU43" s="95"/>
+      <c r="EV43" s="95"/>
+      <c r="EW43" s="96"/>
+      <c r="EX43" s="44">
+        <f t="shared" si="72"/>
+        <v>77</v>
+      </c>
       <c r="EY43" s="44"/>
       <c r="EZ43" s="44"/>
       <c r="FA43" s="44"/>
@@ -11121,20 +11153,20 @@
     </row>
     <row r="44" spans="1:193" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A44" s="17"/>
-      <c r="B44" s="63" t="s">
-        <v>88</v>
-      </c>
-      <c r="C44" s="59" t="s">
-        <v>144</v>
-      </c>
-      <c r="D44" s="30">
-        <v>0</v>
-      </c>
-      <c r="E44" s="38">
-        <v>46175</v>
-      </c>
-      <c r="F44" s="31">
-        <v>46176</v>
+      <c r="B44" s="74" t="s">
+        <v>87</v>
+      </c>
+      <c r="C44" s="91" t="s">
+        <v>139</v>
+      </c>
+      <c r="D44" s="37">
+        <v>1</v>
+      </c>
+      <c r="E44" s="76">
+        <v>46097</v>
+      </c>
+      <c r="F44" s="76">
+        <v>46097</v>
       </c>
       <c r="G44" s="9"/>
       <c r="H44" s="9"/>
@@ -11150,8 +11182,8 @@
       <c r="R44" s="57"/>
       <c r="S44" s="57"/>
       <c r="T44" s="58"/>
-      <c r="U44" s="40"/>
-      <c r="V44" s="40"/>
+      <c r="U44" s="39"/>
+      <c r="V44" s="39"/>
       <c r="W44" s="47"/>
       <c r="X44" s="48"/>
       <c r="Y44" s="48"/>
@@ -11283,7 +11315,10 @@
       <c r="EU44" s="48"/>
       <c r="EV44" s="48"/>
       <c r="EW44" s="49"/>
-      <c r="EX44" s="44"/>
+      <c r="EX44" s="44">
+        <f t="shared" si="72"/>
+        <v>0</v>
+      </c>
       <c r="EY44" s="44"/>
       <c r="EZ44" s="44"/>
       <c r="FA44" s="44"/>
@@ -11326,20 +11361,20 @@
     </row>
     <row r="45" spans="1:193" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A45" s="17"/>
-      <c r="B45" s="63" t="s">
-        <v>85</v>
-      </c>
-      <c r="C45" s="59" t="s">
-        <v>57</v>
-      </c>
-      <c r="D45" s="30">
-        <v>0</v>
-      </c>
-      <c r="E45" s="38">
-        <v>46177</v>
-      </c>
-      <c r="F45" s="31">
-        <v>46178</v>
+      <c r="B45" s="74" t="s">
+        <v>88</v>
+      </c>
+      <c r="C45" s="91" t="s">
+        <v>138</v>
+      </c>
+      <c r="D45" s="37">
+        <v>1</v>
+      </c>
+      <c r="E45" s="76">
+        <v>46097</v>
+      </c>
+      <c r="F45" s="76">
+        <v>46097</v>
       </c>
       <c r="G45" s="9"/>
       <c r="H45" s="9"/>
@@ -11355,8 +11390,8 @@
       <c r="R45" s="57"/>
       <c r="S45" s="57"/>
       <c r="T45" s="58"/>
-      <c r="U45" s="40"/>
-      <c r="V45" s="40"/>
+      <c r="U45" s="39"/>
+      <c r="V45" s="39"/>
       <c r="W45" s="47"/>
       <c r="X45" s="48"/>
       <c r="Y45" s="48"/>
@@ -11531,20 +11566,20 @@
     </row>
     <row r="46" spans="1:193" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A46" s="17"/>
-      <c r="B46" s="63" t="s">
+      <c r="B46" s="74" t="s">
         <v>89</v>
       </c>
-      <c r="C46" s="59" t="s">
-        <v>57</v>
-      </c>
-      <c r="D46" s="30">
-        <v>0</v>
-      </c>
-      <c r="E46" s="38">
-        <v>46178</v>
-      </c>
-      <c r="F46" s="31">
-        <v>46178</v>
+      <c r="C46" s="91" t="s">
+        <v>26</v>
+      </c>
+      <c r="D46" s="37">
+        <v>1</v>
+      </c>
+      <c r="E46" s="76">
+        <v>46097</v>
+      </c>
+      <c r="F46" s="76">
+        <v>46098</v>
       </c>
       <c r="G46" s="9"/>
       <c r="H46" s="9"/>
@@ -11560,8 +11595,8 @@
       <c r="R46" s="57"/>
       <c r="S46" s="57"/>
       <c r="T46" s="58"/>
-      <c r="U46" s="40"/>
-      <c r="V46" s="40"/>
+      <c r="U46" s="39"/>
+      <c r="V46" s="39"/>
       <c r="W46" s="47"/>
       <c r="X46" s="48"/>
       <c r="Y46" s="48"/>
@@ -11735,181 +11770,170 @@
       <c r="GK46" s="44"/>
     </row>
     <row r="47" spans="1:193" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
-      <c r="A47" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="B47" s="85" t="s">
+      <c r="A47" s="17"/>
+      <c r="B47" s="74" t="s">
         <v>90</v>
       </c>
-      <c r="C47" s="86" t="s">
-        <v>57</v>
-      </c>
-      <c r="D47" s="87">
-        <f>SUMPRODUCT(D48:D105,EX48:EX105) / SUM(EX48:EX105)</f>
+      <c r="C47" s="75" t="s">
+        <v>139</v>
+      </c>
+      <c r="D47" s="37">
         <v>1</v>
       </c>
-      <c r="E47" s="88">
-        <f>MIN(E48,E62,E70,E79,E89)</f>
+      <c r="E47" s="76">
         <v>46097</v>
       </c>
-      <c r="F47" s="88">
-        <f>MAX(F48,F62,F70,F89,F79)</f>
-        <v>46183</v>
+      <c r="F47" s="76">
+        <v>46097</v>
       </c>
       <c r="G47" s="9"/>
-      <c r="H47" s="9">
-        <f t="shared" si="71"/>
-        <v>87</v>
-      </c>
-      <c r="I47" s="94"/>
-      <c r="J47" s="95"/>
-      <c r="K47" s="95"/>
-      <c r="L47" s="95"/>
-      <c r="M47" s="96"/>
+      <c r="H47" s="9"/>
+      <c r="I47" s="47"/>
+      <c r="J47" s="48"/>
+      <c r="K47" s="48"/>
+      <c r="L47" s="48"/>
+      <c r="M47" s="49"/>
       <c r="N47" s="39"/>
       <c r="O47" s="39"/>
-      <c r="P47" s="99"/>
-      <c r="Q47" s="100"/>
-      <c r="R47" s="100"/>
-      <c r="S47" s="100"/>
-      <c r="T47" s="101"/>
+      <c r="P47" s="56"/>
+      <c r="Q47" s="57"/>
+      <c r="R47" s="57"/>
+      <c r="S47" s="57"/>
+      <c r="T47" s="58"/>
       <c r="U47" s="39"/>
       <c r="V47" s="39"/>
-      <c r="W47" s="94"/>
-      <c r="X47" s="95"/>
-      <c r="Y47" s="95"/>
-      <c r="Z47" s="95"/>
-      <c r="AA47" s="96"/>
+      <c r="W47" s="47"/>
+      <c r="X47" s="48"/>
+      <c r="Y47" s="48"/>
+      <c r="Z47" s="48"/>
+      <c r="AA47" s="49"/>
       <c r="AB47" s="39"/>
       <c r="AC47" s="39"/>
-      <c r="AD47" s="99"/>
-      <c r="AE47" s="100"/>
-      <c r="AF47" s="100"/>
-      <c r="AG47" s="100"/>
-      <c r="AH47" s="101"/>
+      <c r="AD47" s="56"/>
+      <c r="AE47" s="57"/>
+      <c r="AF47" s="57"/>
+      <c r="AG47" s="57"/>
+      <c r="AH47" s="58"/>
       <c r="AI47" s="39"/>
       <c r="AJ47" s="39"/>
-      <c r="AK47" s="94"/>
-      <c r="AL47" s="95"/>
-      <c r="AM47" s="95"/>
-      <c r="AN47" s="95"/>
-      <c r="AO47" s="96"/>
+      <c r="AK47" s="47"/>
+      <c r="AL47" s="48"/>
+      <c r="AM47" s="48"/>
+      <c r="AN47" s="48"/>
+      <c r="AO47" s="49"/>
       <c r="AP47" s="39"/>
       <c r="AQ47" s="39"/>
-      <c r="AR47" s="99"/>
-      <c r="AS47" s="100"/>
-      <c r="AT47" s="100"/>
-      <c r="AU47" s="100"/>
-      <c r="AV47" s="101"/>
+      <c r="AR47" s="56"/>
+      <c r="AS47" s="57"/>
+      <c r="AT47" s="57"/>
+      <c r="AU47" s="57"/>
+      <c r="AV47" s="58"/>
       <c r="AW47" s="39"/>
       <c r="AX47" s="39"/>
-      <c r="AY47" s="94"/>
-      <c r="AZ47" s="95"/>
-      <c r="BA47" s="95"/>
-      <c r="BB47" s="95"/>
-      <c r="BC47" s="96"/>
+      <c r="AY47" s="47"/>
+      <c r="AZ47" s="48"/>
+      <c r="BA47" s="48"/>
+      <c r="BB47" s="48"/>
+      <c r="BC47" s="49"/>
       <c r="BD47" s="39"/>
       <c r="BE47" s="39"/>
-      <c r="BF47" s="99"/>
-      <c r="BG47" s="100"/>
-      <c r="BH47" s="100"/>
-      <c r="BI47" s="100"/>
-      <c r="BJ47" s="101"/>
+      <c r="BF47" s="56"/>
+      <c r="BG47" s="57"/>
+      <c r="BH47" s="57"/>
+      <c r="BI47" s="57"/>
+      <c r="BJ47" s="58"/>
       <c r="BK47" s="39"/>
       <c r="BL47" s="39"/>
-      <c r="BM47" s="94"/>
-      <c r="BN47" s="95"/>
-      <c r="BO47" s="95"/>
-      <c r="BP47" s="95"/>
-      <c r="BQ47" s="96"/>
+      <c r="BM47" s="47"/>
+      <c r="BN47" s="48"/>
+      <c r="BO47" s="48"/>
+      <c r="BP47" s="48"/>
+      <c r="BQ47" s="49"/>
       <c r="BR47" s="39"/>
       <c r="BS47" s="39"/>
-      <c r="BT47" s="94"/>
-      <c r="BU47" s="95"/>
-      <c r="BV47" s="95"/>
-      <c r="BW47" s="95"/>
-      <c r="BX47" s="96"/>
+      <c r="BT47" s="47"/>
+      <c r="BU47" s="48"/>
+      <c r="BV47" s="48"/>
+      <c r="BW47" s="48"/>
+      <c r="BX47" s="49"/>
       <c r="BY47" s="39"/>
       <c r="BZ47" s="39"/>
-      <c r="CA47" s="99"/>
-      <c r="CB47" s="100"/>
-      <c r="CC47" s="100"/>
-      <c r="CD47" s="100"/>
-      <c r="CE47" s="101"/>
+      <c r="CA47" s="56"/>
+      <c r="CB47" s="57"/>
+      <c r="CC47" s="57"/>
+      <c r="CD47" s="57"/>
+      <c r="CE47" s="58"/>
       <c r="CF47" s="39"/>
       <c r="CG47" s="39"/>
-      <c r="CH47" s="94"/>
-      <c r="CI47" s="95"/>
-      <c r="CJ47" s="95"/>
-      <c r="CK47" s="95"/>
-      <c r="CL47" s="96"/>
+      <c r="CH47" s="47"/>
+      <c r="CI47" s="48"/>
+      <c r="CJ47" s="48"/>
+      <c r="CK47" s="48"/>
+      <c r="CL47" s="49"/>
       <c r="CM47" s="39"/>
       <c r="CN47" s="39"/>
-      <c r="CO47" s="99"/>
-      <c r="CP47" s="100"/>
-      <c r="CQ47" s="100"/>
-      <c r="CR47" s="100"/>
-      <c r="CS47" s="101"/>
+      <c r="CO47" s="56"/>
+      <c r="CP47" s="57"/>
+      <c r="CQ47" s="57"/>
+      <c r="CR47" s="57"/>
+      <c r="CS47" s="58"/>
       <c r="CT47" s="39"/>
       <c r="CU47" s="39"/>
-      <c r="CV47" s="94"/>
-      <c r="CW47" s="95"/>
-      <c r="CX47" s="95"/>
-      <c r="CY47" s="95"/>
-      <c r="CZ47" s="96"/>
+      <c r="CV47" s="47"/>
+      <c r="CW47" s="48"/>
+      <c r="CX47" s="48"/>
+      <c r="CY47" s="48"/>
+      <c r="CZ47" s="49"/>
       <c r="DA47" s="39"/>
       <c r="DB47" s="39"/>
-      <c r="DC47" s="99"/>
-      <c r="DD47" s="100"/>
-      <c r="DE47" s="100"/>
-      <c r="DF47" s="100"/>
-      <c r="DG47" s="101"/>
+      <c r="DC47" s="56"/>
+      <c r="DD47" s="57"/>
+      <c r="DE47" s="57"/>
+      <c r="DF47" s="57"/>
+      <c r="DG47" s="58"/>
       <c r="DH47" s="39"/>
       <c r="DI47" s="39"/>
-      <c r="DJ47" s="94"/>
-      <c r="DK47" s="95"/>
-      <c r="DL47" s="95"/>
-      <c r="DM47" s="95"/>
-      <c r="DN47" s="96"/>
+      <c r="DJ47" s="47"/>
+      <c r="DK47" s="48"/>
+      <c r="DL47" s="48"/>
+      <c r="DM47" s="48"/>
+      <c r="DN47" s="49"/>
       <c r="DO47" s="39"/>
       <c r="DP47" s="39"/>
-      <c r="DQ47" s="99"/>
-      <c r="DR47" s="100"/>
-      <c r="DS47" s="100"/>
-      <c r="DT47" s="100"/>
-      <c r="DU47" s="101"/>
+      <c r="DQ47" s="56"/>
+      <c r="DR47" s="57"/>
+      <c r="DS47" s="57"/>
+      <c r="DT47" s="57"/>
+      <c r="DU47" s="58"/>
       <c r="DV47" s="39"/>
       <c r="DW47" s="39"/>
-      <c r="DX47" s="94"/>
-      <c r="DY47" s="95"/>
-      <c r="DZ47" s="95"/>
-      <c r="EA47" s="95"/>
-      <c r="EB47" s="96"/>
+      <c r="DX47" s="47"/>
+      <c r="DY47" s="48"/>
+      <c r="DZ47" s="48"/>
+      <c r="EA47" s="48"/>
+      <c r="EB47" s="49"/>
       <c r="EC47" s="39"/>
       <c r="ED47" s="39"/>
-      <c r="EE47" s="99"/>
-      <c r="EF47" s="100"/>
-      <c r="EG47" s="100"/>
-      <c r="EH47" s="100"/>
-      <c r="EI47" s="101"/>
+      <c r="EE47" s="56"/>
+      <c r="EF47" s="57"/>
+      <c r="EG47" s="57"/>
+      <c r="EH47" s="57"/>
+      <c r="EI47" s="58"/>
       <c r="EJ47" s="39"/>
       <c r="EK47" s="39"/>
-      <c r="EL47" s="94"/>
-      <c r="EM47" s="95"/>
-      <c r="EN47" s="95"/>
-      <c r="EO47" s="95"/>
-      <c r="EP47" s="96"/>
+      <c r="EL47" s="47"/>
+      <c r="EM47" s="48"/>
+      <c r="EN47" s="48"/>
+      <c r="EO47" s="48"/>
+      <c r="EP47" s="49"/>
       <c r="EQ47" s="39"/>
       <c r="ER47" s="39"/>
-      <c r="ES47" s="94"/>
-      <c r="ET47" s="95"/>
-      <c r="EU47" s="95"/>
-      <c r="EV47" s="95"/>
-      <c r="EW47" s="96"/>
-      <c r="EX47" s="44">
-        <f t="shared" si="72"/>
-        <v>86</v>
-      </c>
+      <c r="ES47" s="47"/>
+      <c r="ET47" s="48"/>
+      <c r="EU47" s="48"/>
+      <c r="EV47" s="48"/>
+      <c r="EW47" s="49"/>
+      <c r="EX47" s="44"/>
       <c r="EY47" s="44"/>
       <c r="EZ47" s="44"/>
       <c r="FA47" s="44"/>
@@ -11952,177 +11976,169 @@
     </row>
     <row r="48" spans="1:193" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A48" s="17"/>
-      <c r="B48" s="70" t="s">
-        <v>158</v>
-      </c>
-      <c r="C48" s="71" t="s">
-        <v>57</v>
-      </c>
-      <c r="D48" s="72">
+      <c r="B48" s="74" t="s">
+        <v>91</v>
+      </c>
+      <c r="C48" s="75" t="s">
+        <v>139</v>
+      </c>
+      <c r="D48" s="37">
         <v>1</v>
       </c>
-      <c r="E48" s="81">
-        <f>MIN(E49:E61)</f>
-        <v>46097</v>
-      </c>
-      <c r="F48" s="82">
-        <f>MAX(F49:F61)</f>
-        <v>46174</v>
+      <c r="E48" s="76">
+        <v>46098</v>
+      </c>
+      <c r="F48" s="76">
+        <v>46098</v>
       </c>
       <c r="G48" s="9"/>
-      <c r="H48" s="9">
-        <f t="shared" si="71"/>
-        <v>78</v>
-      </c>
-      <c r="I48" s="94"/>
-      <c r="J48" s="95"/>
-      <c r="K48" s="95"/>
-      <c r="L48" s="95"/>
-      <c r="M48" s="96"/>
+      <c r="H48" s="9"/>
+      <c r="I48" s="47"/>
+      <c r="J48" s="48"/>
+      <c r="K48" s="48"/>
+      <c r="L48" s="48"/>
+      <c r="M48" s="49"/>
       <c r="N48" s="39"/>
       <c r="O48" s="39"/>
-      <c r="P48" s="99"/>
-      <c r="Q48" s="100"/>
-      <c r="R48" s="100"/>
-      <c r="S48" s="100"/>
-      <c r="T48" s="101"/>
+      <c r="P48" s="56"/>
+      <c r="Q48" s="57"/>
+      <c r="R48" s="57"/>
+      <c r="S48" s="57"/>
+      <c r="T48" s="58"/>
       <c r="U48" s="39"/>
       <c r="V48" s="39"/>
-      <c r="W48" s="94"/>
-      <c r="X48" s="95"/>
-      <c r="Y48" s="95"/>
-      <c r="Z48" s="95"/>
-      <c r="AA48" s="96"/>
+      <c r="W48" s="47"/>
+      <c r="X48" s="48"/>
+      <c r="Y48" s="48"/>
+      <c r="Z48" s="48"/>
+      <c r="AA48" s="49"/>
       <c r="AB48" s="39"/>
       <c r="AC48" s="39"/>
-      <c r="AD48" s="99"/>
-      <c r="AE48" s="100"/>
-      <c r="AF48" s="100"/>
-      <c r="AG48" s="100"/>
-      <c r="AH48" s="101"/>
+      <c r="AD48" s="56"/>
+      <c r="AE48" s="57"/>
+      <c r="AF48" s="57"/>
+      <c r="AG48" s="57"/>
+      <c r="AH48" s="58"/>
       <c r="AI48" s="39"/>
       <c r="AJ48" s="39"/>
-      <c r="AK48" s="94"/>
-      <c r="AL48" s="95"/>
-      <c r="AM48" s="95"/>
-      <c r="AN48" s="95"/>
-      <c r="AO48" s="96"/>
+      <c r="AK48" s="47"/>
+      <c r="AL48" s="48"/>
+      <c r="AM48" s="48"/>
+      <c r="AN48" s="48"/>
+      <c r="AO48" s="49"/>
       <c r="AP48" s="39"/>
       <c r="AQ48" s="39"/>
-      <c r="AR48" s="99"/>
-      <c r="AS48" s="100"/>
-      <c r="AT48" s="100"/>
-      <c r="AU48" s="100"/>
-      <c r="AV48" s="101"/>
+      <c r="AR48" s="56"/>
+      <c r="AS48" s="57"/>
+      <c r="AT48" s="57"/>
+      <c r="AU48" s="57"/>
+      <c r="AV48" s="58"/>
       <c r="AW48" s="39"/>
       <c r="AX48" s="39"/>
-      <c r="AY48" s="94"/>
-      <c r="AZ48" s="95"/>
-      <c r="BA48" s="95"/>
-      <c r="BB48" s="95"/>
-      <c r="BC48" s="96"/>
+      <c r="AY48" s="47"/>
+      <c r="AZ48" s="48"/>
+      <c r="BA48" s="48"/>
+      <c r="BB48" s="48"/>
+      <c r="BC48" s="49"/>
       <c r="BD48" s="39"/>
       <c r="BE48" s="39"/>
-      <c r="BF48" s="99"/>
-      <c r="BG48" s="100"/>
-      <c r="BH48" s="100"/>
-      <c r="BI48" s="100"/>
-      <c r="BJ48" s="101"/>
+      <c r="BF48" s="56"/>
+      <c r="BG48" s="57"/>
+      <c r="BH48" s="57"/>
+      <c r="BI48" s="57"/>
+      <c r="BJ48" s="58"/>
       <c r="BK48" s="39"/>
       <c r="BL48" s="39"/>
-      <c r="BM48" s="94"/>
-      <c r="BN48" s="95"/>
-      <c r="BO48" s="95"/>
-      <c r="BP48" s="95"/>
-      <c r="BQ48" s="96"/>
+      <c r="BM48" s="47"/>
+      <c r="BN48" s="48"/>
+      <c r="BO48" s="48"/>
+      <c r="BP48" s="48"/>
+      <c r="BQ48" s="49"/>
       <c r="BR48" s="39"/>
       <c r="BS48" s="39"/>
-      <c r="BT48" s="94"/>
-      <c r="BU48" s="95"/>
-      <c r="BV48" s="95"/>
-      <c r="BW48" s="95"/>
-      <c r="BX48" s="96"/>
+      <c r="BT48" s="47"/>
+      <c r="BU48" s="48"/>
+      <c r="BV48" s="48"/>
+      <c r="BW48" s="48"/>
+      <c r="BX48" s="49"/>
       <c r="BY48" s="39"/>
       <c r="BZ48" s="39"/>
-      <c r="CA48" s="99"/>
-      <c r="CB48" s="100"/>
-      <c r="CC48" s="100"/>
-      <c r="CD48" s="100"/>
-      <c r="CE48" s="101"/>
+      <c r="CA48" s="56"/>
+      <c r="CB48" s="57"/>
+      <c r="CC48" s="57"/>
+      <c r="CD48" s="57"/>
+      <c r="CE48" s="58"/>
       <c r="CF48" s="39"/>
       <c r="CG48" s="39"/>
-      <c r="CH48" s="94"/>
-      <c r="CI48" s="95"/>
-      <c r="CJ48" s="95"/>
-      <c r="CK48" s="95"/>
-      <c r="CL48" s="96"/>
+      <c r="CH48" s="47"/>
+      <c r="CI48" s="48"/>
+      <c r="CJ48" s="48"/>
+      <c r="CK48" s="48"/>
+      <c r="CL48" s="49"/>
       <c r="CM48" s="39"/>
       <c r="CN48" s="39"/>
-      <c r="CO48" s="99"/>
-      <c r="CP48" s="100"/>
-      <c r="CQ48" s="100"/>
-      <c r="CR48" s="100"/>
-      <c r="CS48" s="101"/>
+      <c r="CO48" s="56"/>
+      <c r="CP48" s="57"/>
+      <c r="CQ48" s="57"/>
+      <c r="CR48" s="57"/>
+      <c r="CS48" s="58"/>
       <c r="CT48" s="39"/>
       <c r="CU48" s="39"/>
-      <c r="CV48" s="94"/>
-      <c r="CW48" s="95"/>
-      <c r="CX48" s="95"/>
-      <c r="CY48" s="95"/>
-      <c r="CZ48" s="96"/>
+      <c r="CV48" s="47"/>
+      <c r="CW48" s="48"/>
+      <c r="CX48" s="48"/>
+      <c r="CY48" s="48"/>
+      <c r="CZ48" s="49"/>
       <c r="DA48" s="39"/>
       <c r="DB48" s="39"/>
-      <c r="DC48" s="99"/>
-      <c r="DD48" s="100"/>
-      <c r="DE48" s="100"/>
-      <c r="DF48" s="100"/>
-      <c r="DG48" s="101"/>
+      <c r="DC48" s="56"/>
+      <c r="DD48" s="57"/>
+      <c r="DE48" s="57"/>
+      <c r="DF48" s="57"/>
+      <c r="DG48" s="58"/>
       <c r="DH48" s="39"/>
       <c r="DI48" s="39"/>
-      <c r="DJ48" s="94"/>
-      <c r="DK48" s="95"/>
-      <c r="DL48" s="95"/>
-      <c r="DM48" s="95"/>
-      <c r="DN48" s="96"/>
+      <c r="DJ48" s="47"/>
+      <c r="DK48" s="48"/>
+      <c r="DL48" s="48"/>
+      <c r="DM48" s="48"/>
+      <c r="DN48" s="49"/>
       <c r="DO48" s="39"/>
       <c r="DP48" s="39"/>
-      <c r="DQ48" s="99"/>
-      <c r="DR48" s="100"/>
-      <c r="DS48" s="100"/>
-      <c r="DT48" s="100"/>
-      <c r="DU48" s="101"/>
+      <c r="DQ48" s="56"/>
+      <c r="DR48" s="57"/>
+      <c r="DS48" s="57"/>
+      <c r="DT48" s="57"/>
+      <c r="DU48" s="58"/>
       <c r="DV48" s="39"/>
       <c r="DW48" s="39"/>
-      <c r="DX48" s="94"/>
-      <c r="DY48" s="95"/>
-      <c r="DZ48" s="95"/>
-      <c r="EA48" s="95"/>
-      <c r="EB48" s="96"/>
+      <c r="DX48" s="47"/>
+      <c r="DY48" s="48"/>
+      <c r="DZ48" s="48"/>
+      <c r="EA48" s="48"/>
+      <c r="EB48" s="49"/>
       <c r="EC48" s="39"/>
       <c r="ED48" s="39"/>
-      <c r="EE48" s="99"/>
-      <c r="EF48" s="100"/>
-      <c r="EG48" s="100"/>
-      <c r="EH48" s="100"/>
-      <c r="EI48" s="101"/>
+      <c r="EE48" s="56"/>
+      <c r="EF48" s="57"/>
+      <c r="EG48" s="57"/>
+      <c r="EH48" s="57"/>
+      <c r="EI48" s="58"/>
       <c r="EJ48" s="39"/>
       <c r="EK48" s="39"/>
-      <c r="EL48" s="94"/>
-      <c r="EM48" s="95"/>
-      <c r="EN48" s="95"/>
-      <c r="EO48" s="95"/>
-      <c r="EP48" s="96"/>
+      <c r="EL48" s="47"/>
+      <c r="EM48" s="48"/>
+      <c r="EN48" s="48"/>
+      <c r="EO48" s="48"/>
+      <c r="EP48" s="49"/>
       <c r="EQ48" s="39"/>
       <c r="ER48" s="39"/>
-      <c r="ES48" s="94"/>
-      <c r="ET48" s="95"/>
-      <c r="EU48" s="95"/>
-      <c r="EV48" s="95"/>
-      <c r="EW48" s="96"/>
-      <c r="EX48" s="44">
-        <f t="shared" si="72"/>
-        <v>77</v>
-      </c>
+      <c r="ES48" s="47"/>
+      <c r="ET48" s="48"/>
+      <c r="EU48" s="48"/>
+      <c r="EV48" s="48"/>
+      <c r="EW48" s="49"/>
+      <c r="EX48" s="44"/>
       <c r="EY48" s="44"/>
       <c r="EZ48" s="44"/>
       <c r="FA48" s="44"/>
@@ -12165,20 +12181,20 @@
     </row>
     <row r="49" spans="1:193" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A49" s="17"/>
-      <c r="B49" s="74" t="s">
-        <v>92</v>
-      </c>
-      <c r="C49" s="91" t="s">
-        <v>144</v>
+      <c r="B49" s="92" t="s">
+        <v>146</v>
+      </c>
+      <c r="C49" s="75" t="s">
+        <v>138</v>
       </c>
       <c r="D49" s="37">
         <v>1</v>
       </c>
       <c r="E49" s="76">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="F49" s="76">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="G49" s="9"/>
       <c r="H49" s="9"/>
@@ -12327,10 +12343,7 @@
       <c r="EU49" s="48"/>
       <c r="EV49" s="48"/>
       <c r="EW49" s="49"/>
-      <c r="EX49" s="44">
-        <f t="shared" si="72"/>
-        <v>0</v>
-      </c>
+      <c r="EX49" s="44"/>
       <c r="EY49" s="44"/>
       <c r="EZ49" s="44"/>
       <c r="FA49" s="44"/>
@@ -12374,19 +12387,19 @@
     <row r="50" spans="1:193" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A50" s="17"/>
       <c r="B50" s="74" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C50" s="91" t="s">
-        <v>143</v>
+        <v>26</v>
       </c>
       <c r="D50" s="37">
         <v>1</v>
       </c>
       <c r="E50" s="76">
-        <v>46097</v>
+        <v>46099</v>
       </c>
       <c r="F50" s="76">
-        <v>46097</v>
+        <v>46174</v>
       </c>
       <c r="G50" s="9"/>
       <c r="H50" s="9"/>
@@ -12579,19 +12592,19 @@
     <row r="51" spans="1:193" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A51" s="17"/>
       <c r="B51" s="74" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C51" s="91" t="s">
-        <v>26</v>
+        <v>139</v>
       </c>
       <c r="D51" s="37">
         <v>1</v>
       </c>
       <c r="E51" s="76">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="F51" s="76">
-        <v>46098</v>
+        <v>46174</v>
       </c>
       <c r="G51" s="9"/>
       <c r="H51" s="9"/>
@@ -12786,17 +12799,17 @@
       <c r="B52" s="74" t="s">
         <v>95</v>
       </c>
-      <c r="C52" s="75" t="s">
-        <v>144</v>
+      <c r="C52" s="91" t="s">
+        <v>26</v>
       </c>
       <c r="D52" s="37">
         <v>1</v>
       </c>
       <c r="E52" s="76">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="F52" s="76">
-        <v>46097</v>
+        <v>46114</v>
       </c>
       <c r="G52" s="9"/>
       <c r="H52" s="9"/>
@@ -12991,17 +13004,17 @@
       <c r="B53" s="74" t="s">
         <v>96</v>
       </c>
-      <c r="C53" s="75" t="s">
-        <v>144</v>
+      <c r="C53" s="91" t="s">
+        <v>147</v>
       </c>
       <c r="D53" s="37">
         <v>1</v>
       </c>
       <c r="E53" s="76">
-        <v>46098</v>
+        <v>46107</v>
       </c>
       <c r="F53" s="76">
-        <v>46098</v>
+        <v>46114</v>
       </c>
       <c r="G53" s="9"/>
       <c r="H53" s="9"/>
@@ -13193,11 +13206,11 @@
     </row>
     <row r="54" spans="1:193" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A54" s="17"/>
-      <c r="B54" s="92" t="s">
-        <v>151</v>
-      </c>
-      <c r="C54" s="75" t="s">
-        <v>143</v>
+      <c r="B54" s="74" t="s">
+        <v>102</v>
+      </c>
+      <c r="C54" s="91" t="s">
+        <v>139</v>
       </c>
       <c r="D54" s="37">
         <v>1</v>
@@ -13205,8 +13218,8 @@
       <c r="E54" s="76">
         <v>46098</v>
       </c>
-      <c r="F54" s="76">
-        <v>46098</v>
+      <c r="F54" s="93">
+        <v>46114</v>
       </c>
       <c r="G54" s="9"/>
       <c r="H54" s="9"/>
@@ -13398,8 +13411,8 @@
     </row>
     <row r="55" spans="1:193" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A55" s="17"/>
-      <c r="B55" s="74" t="s">
-        <v>99</v>
+      <c r="B55" s="92" t="s">
+        <v>148</v>
       </c>
       <c r="C55" s="91" t="s">
         <v>26</v>
@@ -13408,10 +13421,10 @@
         <v>1</v>
       </c>
       <c r="E55" s="76">
-        <v>46099</v>
+        <v>46101</v>
       </c>
       <c r="F55" s="76">
-        <v>46174</v>
+        <v>46101</v>
       </c>
       <c r="G55" s="9"/>
       <c r="H55" s="9"/>
@@ -13604,10 +13617,10 @@
     <row r="56" spans="1:193" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A56" s="17"/>
       <c r="B56" s="74" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="C56" s="91" t="s">
-        <v>144</v>
+        <v>26</v>
       </c>
       <c r="D56" s="37">
         <v>1</v>
@@ -13616,7 +13629,7 @@
         <v>46098</v>
       </c>
       <c r="F56" s="76">
-        <v>46174</v>
+        <v>46100</v>
       </c>
       <c r="G56" s="9"/>
       <c r="H56" s="9"/>
@@ -13808,20 +13821,23 @@
     </row>
     <row r="57" spans="1:193" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A57" s="17"/>
-      <c r="B57" s="74" t="s">
-        <v>100</v>
-      </c>
-      <c r="C57" s="91" t="s">
-        <v>26</v>
-      </c>
-      <c r="D57" s="37">
+      <c r="B57" s="70" t="s">
+        <v>154</v>
+      </c>
+      <c r="C57" s="71" t="s">
+        <v>57</v>
+      </c>
+      <c r="D57" s="72">
+        <f>AVERAGE(D58:D63)</f>
         <v>1</v>
       </c>
-      <c r="E57" s="76">
-        <v>46104</v>
-      </c>
-      <c r="F57" s="76">
-        <v>46114</v>
+      <c r="E57" s="73">
+        <f>MIN(E58:E66)</f>
+        <v>46111</v>
+      </c>
+      <c r="F57" s="73">
+        <f>MAX(F58:F66)</f>
+        <v>46183</v>
       </c>
       <c r="G57" s="9"/>
       <c r="H57" s="9"/>
@@ -13970,7 +13986,10 @@
       <c r="EU57" s="48"/>
       <c r="EV57" s="48"/>
       <c r="EW57" s="49"/>
-      <c r="EX57" s="44"/>
+      <c r="EX57" s="44">
+        <f t="shared" ref="EX57" si="76">IF(OR(F57 = "?",E57 = "?"), 0, F57-E57)</f>
+        <v>72</v>
+      </c>
       <c r="EY57" s="44"/>
       <c r="EZ57" s="44"/>
       <c r="FA57" s="44"/>
@@ -14013,20 +14032,20 @@
     </row>
     <row r="58" spans="1:193" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A58" s="17"/>
-      <c r="B58" s="74" t="s">
-        <v>101</v>
+      <c r="B58" s="92" t="s">
+        <v>150</v>
       </c>
       <c r="C58" s="91" t="s">
-        <v>152</v>
+        <v>26</v>
       </c>
       <c r="D58" s="37">
         <v>1</v>
       </c>
       <c r="E58" s="76">
-        <v>46107</v>
+        <v>46119</v>
       </c>
       <c r="F58" s="76">
-        <v>46114</v>
+        <v>46120</v>
       </c>
       <c r="G58" s="9"/>
       <c r="H58" s="9"/>
@@ -14218,20 +14237,20 @@
     </row>
     <row r="59" spans="1:193" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A59" s="17"/>
-      <c r="B59" s="74" t="s">
-        <v>107</v>
+      <c r="B59" s="92" t="s">
+        <v>151</v>
       </c>
       <c r="C59" s="91" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="D59" s="37">
         <v>1</v>
       </c>
       <c r="E59" s="76">
-        <v>46098</v>
-      </c>
-      <c r="F59" s="93">
-        <v>46114</v>
+        <v>46119</v>
+      </c>
+      <c r="F59" s="76">
+        <v>46120</v>
       </c>
       <c r="G59" s="9"/>
       <c r="H59" s="9"/>
@@ -14423,20 +14442,20 @@
     </row>
     <row r="60" spans="1:193" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A60" s="17"/>
-      <c r="B60" s="92" t="s">
-        <v>153</v>
+      <c r="B60" s="74" t="s">
+        <v>105</v>
       </c>
       <c r="C60" s="91" t="s">
-        <v>26</v>
+        <v>138</v>
       </c>
       <c r="D60" s="37">
         <v>1</v>
       </c>
       <c r="E60" s="76">
-        <v>46101</v>
+        <v>46163</v>
       </c>
       <c r="F60" s="76">
-        <v>46101</v>
+        <v>46163</v>
       </c>
       <c r="G60" s="9"/>
       <c r="H60" s="9"/>
@@ -14629,19 +14648,19 @@
     <row r="61" spans="1:193" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A61" s="17"/>
       <c r="B61" s="74" t="s">
-        <v>108</v>
-      </c>
-      <c r="C61" s="91" t="s">
-        <v>26</v>
+        <v>106</v>
+      </c>
+      <c r="C61" s="75" t="s">
+        <v>138</v>
       </c>
       <c r="D61" s="37">
         <v>1</v>
       </c>
       <c r="E61" s="76">
-        <v>46098</v>
+        <v>46163</v>
       </c>
       <c r="F61" s="76">
-        <v>46100</v>
+        <v>46163</v>
       </c>
       <c r="G61" s="9"/>
       <c r="H61" s="9"/>
@@ -14833,23 +14852,20 @@
     </row>
     <row r="62" spans="1:193" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A62" s="17"/>
-      <c r="B62" s="70" t="s">
-        <v>159</v>
-      </c>
-      <c r="C62" s="71" t="s">
-        <v>57</v>
-      </c>
-      <c r="D62" s="72">
-        <f>AVERAGE(D63:D68)</f>
+      <c r="B62" s="92" t="s">
+        <v>93</v>
+      </c>
+      <c r="C62" s="91" t="s">
+        <v>149</v>
+      </c>
+      <c r="D62" s="37">
         <v>1</v>
       </c>
-      <c r="E62" s="73">
-        <f>MIN(E63:E69)</f>
+      <c r="E62" s="76">
         <v>46111</v>
       </c>
-      <c r="F62" s="73">
-        <f>MAX(F63:F69)</f>
-        <v>46183</v>
+      <c r="F62" s="76">
+        <v>46112</v>
       </c>
       <c r="G62" s="9"/>
       <c r="H62" s="9"/>
@@ -14998,10 +15014,7 @@
       <c r="EU62" s="48"/>
       <c r="EV62" s="48"/>
       <c r="EW62" s="49"/>
-      <c r="EX62" s="44">
-        <f t="shared" ref="EX62" si="76">IF(OR(F62 = "?",E62 = "?"), 0, F62-E62)</f>
-        <v>72</v>
-      </c>
+      <c r="EX62" s="44"/>
       <c r="EY62" s="44"/>
       <c r="EZ62" s="44"/>
       <c r="FA62" s="44"/>
@@ -15045,19 +15058,19 @@
     <row r="63" spans="1:193" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A63" s="17"/>
       <c r="B63" s="92" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C63" s="91" t="s">
-        <v>26</v>
+        <v>138</v>
       </c>
       <c r="D63" s="37">
         <v>1</v>
       </c>
       <c r="E63" s="76">
-        <v>46119</v>
+        <v>46174</v>
       </c>
       <c r="F63" s="76">
-        <v>46120</v>
+        <v>46183</v>
       </c>
       <c r="G63" s="9"/>
       <c r="H63" s="9"/>
@@ -15249,20 +15262,20 @@
     </row>
     <row r="64" spans="1:193" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A64" s="17"/>
-      <c r="B64" s="92" t="s">
+      <c r="B64" s="118" t="s">
         <v>156</v>
       </c>
-      <c r="C64" s="91" t="s">
-        <v>143</v>
+      <c r="C64" s="119" t="s">
+        <v>26</v>
       </c>
       <c r="D64" s="37">
         <v>1</v>
       </c>
       <c r="E64" s="76">
-        <v>46119</v>
+        <v>46143</v>
       </c>
       <c r="F64" s="76">
-        <v>46120</v>
+        <v>46152</v>
       </c>
       <c r="G64" s="9"/>
       <c r="H64" s="9"/>
@@ -15453,21 +15466,23 @@
       <c r="GK64" s="44"/>
     </row>
     <row r="65" spans="1:193" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
-      <c r="A65" s="17"/>
-      <c r="B65" s="74" t="s">
-        <v>110</v>
-      </c>
-      <c r="C65" s="91" t="s">
-        <v>143</v>
+      <c r="A65" s="17" t="s">
+        <v>157</v>
+      </c>
+      <c r="B65" s="118" t="s">
+        <v>158</v>
+      </c>
+      <c r="C65" s="119" t="s">
+        <v>26</v>
       </c>
       <c r="D65" s="37">
         <v>1</v>
       </c>
       <c r="E65" s="76">
-        <v>46163</v>
+        <v>46174</v>
       </c>
       <c r="F65" s="76">
-        <v>46163</v>
+        <v>46183</v>
       </c>
       <c r="G65" s="9"/>
       <c r="H65" s="9"/>
@@ -15659,20 +15674,20 @@
     </row>
     <row r="66" spans="1:193" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A66" s="17"/>
-      <c r="B66" s="74" t="s">
-        <v>111</v>
-      </c>
-      <c r="C66" s="75" t="s">
-        <v>143</v>
+      <c r="B66" s="92" t="s">
+        <v>115</v>
+      </c>
+      <c r="C66" s="91" t="s">
+        <v>141</v>
       </c>
       <c r="D66" s="37">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E66" s="76">
-        <v>46163</v>
-      </c>
-      <c r="F66" s="76">
-        <v>46163</v>
+        <v>46174</v>
+      </c>
+      <c r="F66" s="93" t="s">
+        <v>155</v>
       </c>
       <c r="G66" s="9"/>
       <c r="H66" s="9"/>
@@ -15864,21 +15879,18 @@
     </row>
     <row r="67" spans="1:193" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A67" s="17"/>
-      <c r="B67" s="92" t="s">
-        <v>98</v>
-      </c>
-      <c r="C67" s="91" t="s">
-        <v>154</v>
-      </c>
-      <c r="D67" s="37">
-        <v>1</v>
-      </c>
-      <c r="E67" s="76">
-        <v>46111</v>
-      </c>
-      <c r="F67" s="76">
-        <v>46112</v>
-      </c>
+      <c r="B67" s="70" t="s">
+        <v>101</v>
+      </c>
+      <c r="C67" s="71" t="s">
+        <v>57</v>
+      </c>
+      <c r="D67" s="72">
+        <f>AVERAGE(D68:D108)</f>
+        <v>0</v>
+      </c>
+      <c r="E67" s="73"/>
+      <c r="F67" s="73"/>
       <c r="G67" s="9"/>
       <c r="H67" s="9"/>
       <c r="I67" s="47"/>
@@ -16026,7 +16038,10 @@
       <c r="EU67" s="48"/>
       <c r="EV67" s="48"/>
       <c r="EW67" s="49"/>
-      <c r="EX67" s="44"/>
+      <c r="EX67" s="44">
+        <f t="shared" ref="EX67" si="77">IF(OR(F67 = "?",E67 = "?"), 0, F67-E67)</f>
+        <v>0</v>
+      </c>
       <c r="EY67" s="44"/>
       <c r="EZ67" s="44"/>
       <c r="FA67" s="44"/>
@@ -16069,21 +16084,17 @@
     </row>
     <row r="68" spans="1:193" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A68" s="17"/>
-      <c r="B68" s="92" t="s">
-        <v>157</v>
-      </c>
-      <c r="C68" s="91" t="s">
-        <v>143</v>
+      <c r="B68" s="74" t="s">
+        <v>107</v>
+      </c>
+      <c r="C68" s="75" t="s">
+        <v>139</v>
       </c>
       <c r="D68" s="37">
-        <v>1</v>
-      </c>
-      <c r="E68" s="76">
-        <v>46174</v>
-      </c>
-      <c r="F68" s="76">
-        <v>46183</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E68" s="76"/>
+      <c r="F68" s="76"/>
       <c r="G68" s="9"/>
       <c r="H68" s="9"/>
       <c r="I68" s="47"/>
@@ -16274,21 +16285,17 @@
     </row>
     <row r="69" spans="1:193" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A69" s="17"/>
-      <c r="B69" s="92" t="s">
-        <v>120</v>
-      </c>
-      <c r="C69" s="91" t="s">
-        <v>146</v>
+      <c r="B69" s="74" t="s">
+        <v>108</v>
+      </c>
+      <c r="C69" s="75" t="s">
+        <v>138</v>
       </c>
       <c r="D69" s="37">
-        <v>0.5</v>
-      </c>
-      <c r="E69" s="76">
-        <v>46174</v>
-      </c>
-      <c r="F69" s="93" t="s">
-        <v>160</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E69" s="76"/>
+      <c r="F69" s="76"/>
       <c r="G69" s="9"/>
       <c r="H69" s="9"/>
       <c r="I69" s="47"/>
@@ -16479,18 +16486,17 @@
     </row>
     <row r="70" spans="1:193" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A70" s="17"/>
-      <c r="B70" s="70" t="s">
-        <v>106</v>
-      </c>
-      <c r="C70" s="71" t="s">
-        <v>57</v>
-      </c>
-      <c r="D70" s="72">
-        <f>AVERAGE(D71:D111)</f>
+      <c r="B70" s="74" t="s">
+        <v>110</v>
+      </c>
+      <c r="C70" s="75" t="s">
+        <v>26</v>
+      </c>
+      <c r="D70" s="37">
         <v>0</v>
       </c>
-      <c r="E70" s="73"/>
-      <c r="F70" s="73"/>
+      <c r="E70" s="76"/>
+      <c r="F70" s="76"/>
       <c r="G70" s="9"/>
       <c r="H70" s="9"/>
       <c r="I70" s="47"/>
@@ -16638,10 +16644,7 @@
       <c r="EU70" s="48"/>
       <c r="EV70" s="48"/>
       <c r="EW70" s="49"/>
-      <c r="EX70" s="44">
-        <f t="shared" ref="EX70" si="77">IF(OR(F70 = "?",E70 = "?"), 0, F70-E70)</f>
-        <v>0</v>
-      </c>
+      <c r="EX70" s="44"/>
       <c r="EY70" s="44"/>
       <c r="EZ70" s="44"/>
       <c r="FA70" s="44"/>
@@ -16685,10 +16688,10 @@
     <row r="71" spans="1:193" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A71" s="17"/>
       <c r="B71" s="74" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C71" s="75" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="D71" s="37">
         <v>0</v>
@@ -16886,10 +16889,10 @@
     <row r="72" spans="1:193" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A72" s="17"/>
       <c r="B72" s="74" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C72" s="75" t="s">
-        <v>143</v>
+        <v>26</v>
       </c>
       <c r="D72" s="37">
         <v>0</v>
@@ -17087,10 +17090,10 @@
     <row r="73" spans="1:193" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A73" s="17"/>
       <c r="B73" s="74" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C73" s="75" t="s">
-        <v>26</v>
+        <v>138</v>
       </c>
       <c r="D73" s="37">
         <v>0</v>
@@ -17291,7 +17294,7 @@
         <v>114</v>
       </c>
       <c r="C74" s="75" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="D74" s="37">
         <v>0</v>
@@ -17489,7 +17492,7 @@
     <row r="75" spans="1:193" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A75" s="17"/>
       <c r="B75" s="74" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C75" s="75" t="s">
         <v>26</v>
@@ -17689,17 +17692,18 @@
     </row>
     <row r="76" spans="1:193" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A76" s="17"/>
-      <c r="B76" s="74" t="s">
-        <v>118</v>
-      </c>
-      <c r="C76" s="75" t="s">
-        <v>143</v>
-      </c>
-      <c r="D76" s="37">
+      <c r="B76" s="70" t="s">
+        <v>104</v>
+      </c>
+      <c r="C76" s="71" t="s">
+        <v>57</v>
+      </c>
+      <c r="D76" s="72">
+        <f>AVERAGE(D77:D111)</f>
         <v>0</v>
       </c>
-      <c r="E76" s="76"/>
-      <c r="F76" s="76"/>
+      <c r="E76" s="73"/>
+      <c r="F76" s="73"/>
       <c r="G76" s="9"/>
       <c r="H76" s="9"/>
       <c r="I76" s="47"/>
@@ -17847,7 +17851,10 @@
       <c r="EU76" s="48"/>
       <c r="EV76" s="48"/>
       <c r="EW76" s="49"/>
-      <c r="EX76" s="44"/>
+      <c r="EX76" s="44">
+        <f t="shared" ref="EX76" si="78">IF(OR(F76 = "?",E76 = "?"), 0, F76-E76)</f>
+        <v>0</v>
+      </c>
       <c r="EY76" s="44"/>
       <c r="EZ76" s="44"/>
       <c r="FA76" s="44"/>
@@ -17891,10 +17898,10 @@
     <row r="77" spans="1:193" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A77" s="17"/>
       <c r="B77" s="74" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C77" s="75" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="D77" s="37">
         <v>0</v>
@@ -18092,10 +18099,10 @@
     <row r="78" spans="1:193" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A78" s="17"/>
       <c r="B78" s="74" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C78" s="75" t="s">
-        <v>26</v>
+        <v>138</v>
       </c>
       <c r="D78" s="37">
         <v>0</v>
@@ -18292,18 +18299,17 @@
     </row>
     <row r="79" spans="1:193" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A79" s="17"/>
-      <c r="B79" s="70" t="s">
-        <v>109</v>
-      </c>
-      <c r="C79" s="71" t="s">
-        <v>57</v>
-      </c>
-      <c r="D79" s="72">
-        <f>AVERAGE(D80:D114)</f>
+      <c r="B79" s="74" t="s">
+        <v>120</v>
+      </c>
+      <c r="C79" s="75" t="s">
+        <v>26</v>
+      </c>
+      <c r="D79" s="37">
         <v>0</v>
       </c>
-      <c r="E79" s="73"/>
-      <c r="F79" s="73"/>
+      <c r="E79" s="76"/>
+      <c r="F79" s="76"/>
       <c r="G79" s="9"/>
       <c r="H79" s="9"/>
       <c r="I79" s="47"/>
@@ -18451,10 +18457,7 @@
       <c r="EU79" s="48"/>
       <c r="EV79" s="48"/>
       <c r="EW79" s="49"/>
-      <c r="EX79" s="44">
-        <f t="shared" ref="EX79" si="78">IF(OR(F79 = "?",E79 = "?"), 0, F79-E79)</f>
-        <v>0</v>
-      </c>
+      <c r="EX79" s="44"/>
       <c r="EY79" s="44"/>
       <c r="EZ79" s="44"/>
       <c r="FA79" s="44"/>
@@ -18498,10 +18501,10 @@
     <row r="80" spans="1:193" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A80" s="17"/>
       <c r="B80" s="74" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C80" s="75" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="D80" s="37">
         <v>0</v>
@@ -18699,10 +18702,10 @@
     <row r="81" spans="1:193" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A81" s="17"/>
       <c r="B81" s="74" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C81" s="75" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D81" s="37">
         <v>0</v>
@@ -18900,10 +18903,10 @@
     <row r="82" spans="1:193" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A82" s="17"/>
       <c r="B82" s="74" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="C82" s="75" t="s">
-        <v>26</v>
+        <v>138</v>
       </c>
       <c r="D82" s="37">
         <v>0</v>
@@ -19101,10 +19104,10 @@
     <row r="83" spans="1:193" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A83" s="17"/>
       <c r="B83" s="74" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C83" s="75" t="s">
-        <v>144</v>
+        <v>26</v>
       </c>
       <c r="D83" s="37">
         <v>0</v>
@@ -19302,10 +19305,10 @@
     <row r="84" spans="1:193" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A84" s="17"/>
       <c r="B84" s="74" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C84" s="75" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D84" s="37">
         <v>0</v>
@@ -19506,7 +19509,7 @@
         <v>123</v>
       </c>
       <c r="C85" s="75" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D85" s="37">
         <v>0</v>
@@ -19703,17 +19706,18 @@
     </row>
     <row r="86" spans="1:193" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A86" s="17"/>
-      <c r="B86" s="74" t="s">
-        <v>127</v>
-      </c>
-      <c r="C86" s="75" t="s">
-        <v>26</v>
-      </c>
-      <c r="D86" s="37">
+      <c r="B86" s="70" t="s">
+        <v>100</v>
+      </c>
+      <c r="C86" s="71" t="s">
+        <v>57</v>
+      </c>
+      <c r="D86" s="72">
+        <f>AVERAGE(D87:D114)</f>
         <v>0</v>
       </c>
-      <c r="E86" s="76"/>
-      <c r="F86" s="76"/>
+      <c r="E86" s="81"/>
+      <c r="F86" s="73"/>
       <c r="G86" s="9"/>
       <c r="H86" s="9"/>
       <c r="I86" s="47"/>
@@ -19861,7 +19865,10 @@
       <c r="EU86" s="48"/>
       <c r="EV86" s="48"/>
       <c r="EW86" s="49"/>
-      <c r="EX86" s="44"/>
+      <c r="EX86" s="44">
+        <f t="shared" ref="EX86" si="79">IF(OR(F86 = "?",E86 = "?"), 0, F86-E86)</f>
+        <v>0</v>
+      </c>
       <c r="EY86" s="44"/>
       <c r="EZ86" s="44"/>
       <c r="FA86" s="44"/>
@@ -19905,10 +19912,10 @@
     <row r="87" spans="1:193" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A87" s="17"/>
       <c r="B87" s="74" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C87" s="75" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="D87" s="37">
         <v>0</v>
@@ -20106,10 +20113,10 @@
     <row r="88" spans="1:193" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A88" s="17"/>
       <c r="B88" s="74" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C88" s="75" t="s">
-        <v>144</v>
+        <v>26</v>
       </c>
       <c r="D88" s="37">
         <v>0</v>
@@ -20306,18 +20313,17 @@
     </row>
     <row r="89" spans="1:193" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A89" s="17"/>
-      <c r="B89" s="70" t="s">
-        <v>105</v>
-      </c>
-      <c r="C89" s="71" t="s">
-        <v>57</v>
-      </c>
-      <c r="D89" s="72">
-        <f>AVERAGE(D90:D117)</f>
+      <c r="B89" s="74" t="s">
+        <v>124</v>
+      </c>
+      <c r="C89" s="75" t="s">
+        <v>139</v>
+      </c>
+      <c r="D89" s="37">
         <v>0</v>
       </c>
-      <c r="E89" s="81"/>
-      <c r="F89" s="73"/>
+      <c r="E89" s="76"/>
+      <c r="F89" s="76"/>
       <c r="G89" s="9"/>
       <c r="H89" s="9"/>
       <c r="I89" s="47"/>
@@ -20465,10 +20471,7 @@
       <c r="EU89" s="48"/>
       <c r="EV89" s="48"/>
       <c r="EW89" s="49"/>
-      <c r="EX89" s="44">
-        <f t="shared" ref="EX89" si="79">IF(OR(F89 = "?",E89 = "?"), 0, F89-E89)</f>
-        <v>0</v>
-      </c>
+      <c r="EX89" s="44"/>
       <c r="EY89" s="44"/>
       <c r="EZ89" s="44"/>
       <c r="FA89" s="44"/>
@@ -20512,10 +20515,10 @@
     <row r="90" spans="1:193" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A90" s="17"/>
       <c r="B90" s="74" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C90" s="75" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D90" s="37">
         <v>0</v>
@@ -20713,10 +20716,10 @@
     <row r="91" spans="1:193" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A91" s="17"/>
       <c r="B91" s="74" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C91" s="75" t="s">
-        <v>26</v>
+        <v>139</v>
       </c>
       <c r="D91" s="37">
         <v>0</v>
@@ -20917,7 +20920,7 @@
         <v>129</v>
       </c>
       <c r="C92" s="75" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="D92" s="37">
         <v>0</v>
@@ -21115,10 +21118,10 @@
     <row r="93" spans="1:193" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A93" s="17"/>
       <c r="B93" s="74" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="C93" s="75" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D93" s="37">
         <v>0</v>
@@ -21316,10 +21319,10 @@
     <row r="94" spans="1:193" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A94" s="17"/>
       <c r="B94" s="74" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="C94" s="75" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D94" s="37">
         <v>0</v>
@@ -21517,11 +21520,9 @@
     <row r="95" spans="1:193" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A95" s="17"/>
       <c r="B95" s="74" t="s">
-        <v>134</v>
-      </c>
-      <c r="C95" s="75" t="s">
-        <v>143</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="C95" s="75"/>
       <c r="D95" s="37">
         <v>0</v>
       </c>
@@ -21717,17 +21718,22 @@
     </row>
     <row r="96" spans="1:193" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A96" s="17"/>
-      <c r="B96" s="74" t="s">
-        <v>131</v>
-      </c>
-      <c r="C96" s="75" t="s">
-        <v>144</v>
-      </c>
-      <c r="D96" s="37">
+      <c r="B96" s="70" t="s">
+        <v>86</v>
+      </c>
+      <c r="C96" s="71" t="s">
+        <v>57</v>
+      </c>
+      <c r="D96" s="72">
+        <f>AVERAGE(D97:D102)</f>
         <v>0</v>
       </c>
-      <c r="E96" s="76"/>
-      <c r="F96" s="76"/>
+      <c r="E96" s="81" t="s">
+        <v>27</v>
+      </c>
+      <c r="F96" s="81" t="s">
+        <v>27</v>
+      </c>
       <c r="G96" s="9"/>
       <c r="H96" s="9"/>
       <c r="I96" s="47"/>
@@ -21875,7 +21881,10 @@
       <c r="EU96" s="48"/>
       <c r="EV96" s="48"/>
       <c r="EW96" s="49"/>
-      <c r="EX96" s="44"/>
+      <c r="EX96" s="44">
+        <f t="shared" ref="EX96" si="80">IF(OR(F96 = "?",E96 = "?"), 0, F96-E96)</f>
+        <v>0</v>
+      </c>
       <c r="EY96" s="44"/>
       <c r="EZ96" s="44"/>
       <c r="FA96" s="44"/>
@@ -21919,16 +21928,20 @@
     <row r="97" spans="1:193" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A97" s="17"/>
       <c r="B97" s="74" t="s">
-        <v>147</v>
-      </c>
-      <c r="C97" s="75" t="s">
-        <v>148</v>
+        <v>132</v>
+      </c>
+      <c r="C97" s="83" t="s">
+        <v>27</v>
       </c>
       <c r="D97" s="37">
         <v>0</v>
       </c>
-      <c r="E97" s="76"/>
-      <c r="F97" s="76"/>
+      <c r="E97" s="84" t="s">
+        <v>27</v>
+      </c>
+      <c r="F97" s="84" t="s">
+        <v>27</v>
+      </c>
       <c r="G97" s="9"/>
       <c r="H97" s="9"/>
       <c r="I97" s="47"/>
@@ -22120,14 +22133,20 @@
     <row r="98" spans="1:193" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A98" s="17"/>
       <c r="B98" s="74" t="s">
-        <v>136</v>
-      </c>
-      <c r="C98" s="75"/>
+        <v>133</v>
+      </c>
+      <c r="C98" s="83" t="s">
+        <v>27</v>
+      </c>
       <c r="D98" s="37">
         <v>0</v>
       </c>
-      <c r="E98" s="76"/>
-      <c r="F98" s="76"/>
+      <c r="E98" s="84" t="s">
+        <v>27</v>
+      </c>
+      <c r="F98" s="84" t="s">
+        <v>27</v>
+      </c>
       <c r="G98" s="9"/>
       <c r="H98" s="9"/>
       <c r="I98" s="47"/>
@@ -22318,20 +22337,19 @@
     </row>
     <row r="99" spans="1:193" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A99" s="17"/>
-      <c r="B99" s="70" t="s">
-        <v>91</v>
-      </c>
-      <c r="C99" s="71" t="s">
-        <v>57</v>
-      </c>
-      <c r="D99" s="72">
-        <f>AVERAGE(D100:D105)</f>
+      <c r="B99" s="74" t="s">
+        <v>134</v>
+      </c>
+      <c r="C99" s="83" t="s">
+        <v>27</v>
+      </c>
+      <c r="D99" s="37">
         <v>0</v>
       </c>
-      <c r="E99" s="81" t="s">
+      <c r="E99" s="84" t="s">
         <v>27</v>
       </c>
-      <c r="F99" s="81" t="s">
+      <c r="F99" s="84" t="s">
         <v>27</v>
       </c>
       <c r="G99" s="9"/>
@@ -22481,10 +22499,7 @@
       <c r="EU99" s="48"/>
       <c r="EV99" s="48"/>
       <c r="EW99" s="49"/>
-      <c r="EX99" s="44">
-        <f t="shared" ref="EX99" si="80">IF(OR(F99 = "?",E99 = "?"), 0, F99-E99)</f>
-        <v>0</v>
-      </c>
+      <c r="EX99" s="44"/>
       <c r="EY99" s="44"/>
       <c r="EZ99" s="44"/>
       <c r="FA99" s="44"/>
@@ -22528,7 +22543,7 @@
     <row r="100" spans="1:193" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A100" s="17"/>
       <c r="B100" s="74" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C100" s="83" t="s">
         <v>27</v>
@@ -22733,7 +22748,7 @@
     <row r="101" spans="1:193" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A101" s="17"/>
       <c r="B101" s="74" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C101" s="83" t="s">
         <v>27</v>
@@ -22938,7 +22953,7 @@
     <row r="102" spans="1:193" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
       <c r="A102" s="17"/>
       <c r="B102" s="74" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C102" s="83" t="s">
         <v>27</v>
@@ -23141,169 +23156,164 @@
       <c r="GK102" s="44"/>
     </row>
     <row r="103" spans="1:193" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
-      <c r="A103" s="17"/>
-      <c r="B103" s="74" t="s">
-        <v>140</v>
-      </c>
-      <c r="C103" s="83" t="s">
-        <v>27</v>
-      </c>
-      <c r="D103" s="37">
-        <v>0</v>
-      </c>
-      <c r="E103" s="84" t="s">
-        <v>27</v>
-      </c>
-      <c r="F103" s="84" t="s">
-        <v>27</v>
-      </c>
+      <c r="A103" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="B103" s="21"/>
+      <c r="C103" s="20"/>
+      <c r="D103" s="8"/>
+      <c r="E103" s="23"/>
+      <c r="F103" s="23"/>
       <c r="G103" s="9"/>
-      <c r="H103" s="9"/>
-      <c r="I103" s="47"/>
-      <c r="J103" s="48"/>
-      <c r="K103" s="48"/>
-      <c r="L103" s="48"/>
-      <c r="M103" s="49"/>
-      <c r="N103" s="39"/>
-      <c r="O103" s="39"/>
-      <c r="P103" s="56"/>
-      <c r="Q103" s="57"/>
-      <c r="R103" s="57"/>
-      <c r="S103" s="57"/>
-      <c r="T103" s="58"/>
-      <c r="U103" s="39"/>
-      <c r="V103" s="39"/>
-      <c r="W103" s="47"/>
-      <c r="X103" s="48"/>
-      <c r="Y103" s="48"/>
-      <c r="Z103" s="48"/>
-      <c r="AA103" s="49"/>
-      <c r="AB103" s="39"/>
-      <c r="AC103" s="39"/>
-      <c r="AD103" s="56"/>
-      <c r="AE103" s="57"/>
-      <c r="AF103" s="57"/>
-      <c r="AG103" s="57"/>
-      <c r="AH103" s="58"/>
-      <c r="AI103" s="39"/>
-      <c r="AJ103" s="39"/>
-      <c r="AK103" s="47"/>
-      <c r="AL103" s="48"/>
-      <c r="AM103" s="48"/>
-      <c r="AN103" s="48"/>
-      <c r="AO103" s="49"/>
-      <c r="AP103" s="39"/>
-      <c r="AQ103" s="39"/>
-      <c r="AR103" s="56"/>
-      <c r="AS103" s="57"/>
-      <c r="AT103" s="57"/>
-      <c r="AU103" s="57"/>
-      <c r="AV103" s="58"/>
-      <c r="AW103" s="39"/>
-      <c r="AX103" s="39"/>
-      <c r="AY103" s="47"/>
-      <c r="AZ103" s="48"/>
-      <c r="BA103" s="48"/>
-      <c r="BB103" s="48"/>
-      <c r="BC103" s="49"/>
-      <c r="BD103" s="39"/>
-      <c r="BE103" s="39"/>
-      <c r="BF103" s="56"/>
-      <c r="BG103" s="57"/>
-      <c r="BH103" s="57"/>
-      <c r="BI103" s="57"/>
-      <c r="BJ103" s="58"/>
-      <c r="BK103" s="39"/>
-      <c r="BL103" s="39"/>
-      <c r="BM103" s="47"/>
-      <c r="BN103" s="48"/>
-      <c r="BO103" s="48"/>
-      <c r="BP103" s="48"/>
-      <c r="BQ103" s="49"/>
-      <c r="BR103" s="39"/>
-      <c r="BS103" s="39"/>
-      <c r="BT103" s="47"/>
-      <c r="BU103" s="48"/>
-      <c r="BV103" s="48"/>
-      <c r="BW103" s="48"/>
-      <c r="BX103" s="49"/>
-      <c r="BY103" s="39"/>
-      <c r="BZ103" s="39"/>
-      <c r="CA103" s="56"/>
-      <c r="CB103" s="57"/>
-      <c r="CC103" s="57"/>
-      <c r="CD103" s="57"/>
-      <c r="CE103" s="58"/>
-      <c r="CF103" s="39"/>
-      <c r="CG103" s="39"/>
-      <c r="CH103" s="47"/>
-      <c r="CI103" s="48"/>
-      <c r="CJ103" s="48"/>
-      <c r="CK103" s="48"/>
-      <c r="CL103" s="49"/>
-      <c r="CM103" s="39"/>
-      <c r="CN103" s="39"/>
-      <c r="CO103" s="56"/>
-      <c r="CP103" s="57"/>
-      <c r="CQ103" s="57"/>
-      <c r="CR103" s="57"/>
-      <c r="CS103" s="58"/>
-      <c r="CT103" s="39"/>
-      <c r="CU103" s="39"/>
-      <c r="CV103" s="47"/>
-      <c r="CW103" s="48"/>
-      <c r="CX103" s="48"/>
-      <c r="CY103" s="48"/>
-      <c r="CZ103" s="49"/>
-      <c r="DA103" s="39"/>
-      <c r="DB103" s="39"/>
-      <c r="DC103" s="56"/>
-      <c r="DD103" s="57"/>
-      <c r="DE103" s="57"/>
-      <c r="DF103" s="57"/>
-      <c r="DG103" s="58"/>
-      <c r="DH103" s="39"/>
-      <c r="DI103" s="39"/>
-      <c r="DJ103" s="47"/>
-      <c r="DK103" s="48"/>
-      <c r="DL103" s="48"/>
-      <c r="DM103" s="48"/>
-      <c r="DN103" s="49"/>
-      <c r="DO103" s="39"/>
-      <c r="DP103" s="39"/>
-      <c r="DQ103" s="56"/>
-      <c r="DR103" s="57"/>
-      <c r="DS103" s="57"/>
-      <c r="DT103" s="57"/>
-      <c r="DU103" s="58"/>
-      <c r="DV103" s="39"/>
-      <c r="DW103" s="39"/>
-      <c r="DX103" s="47"/>
-      <c r="DY103" s="48"/>
-      <c r="DZ103" s="48"/>
-      <c r="EA103" s="48"/>
-      <c r="EB103" s="49"/>
-      <c r="EC103" s="39"/>
-      <c r="ED103" s="39"/>
-      <c r="EE103" s="56"/>
-      <c r="EF103" s="57"/>
-      <c r="EG103" s="57"/>
-      <c r="EH103" s="57"/>
-      <c r="EI103" s="58"/>
-      <c r="EJ103" s="39"/>
-      <c r="EK103" s="39"/>
-      <c r="EL103" s="47"/>
-      <c r="EM103" s="48"/>
-      <c r="EN103" s="48"/>
-      <c r="EO103" s="48"/>
-      <c r="EP103" s="49"/>
-      <c r="EQ103" s="39"/>
-      <c r="ER103" s="39"/>
-      <c r="ES103" s="47"/>
-      <c r="ET103" s="48"/>
-      <c r="EU103" s="48"/>
-      <c r="EV103" s="48"/>
-      <c r="EW103" s="49"/>
+      <c r="H103" s="9" t="str">
+        <f t="shared" si="71"/>
+        <v/>
+      </c>
+      <c r="I103" s="14"/>
+      <c r="J103" s="14"/>
+      <c r="K103" s="14"/>
+      <c r="L103" s="14"/>
+      <c r="M103" s="14"/>
+      <c r="N103" s="14"/>
+      <c r="O103" s="14"/>
+      <c r="P103" s="14"/>
+      <c r="Q103" s="14"/>
+      <c r="R103" s="14"/>
+      <c r="S103" s="14"/>
+      <c r="T103" s="14"/>
+      <c r="U103" s="14"/>
+      <c r="V103" s="14"/>
+      <c r="W103" s="14"/>
+      <c r="X103" s="14"/>
+      <c r="Y103" s="14"/>
+      <c r="Z103" s="14"/>
+      <c r="AA103" s="14"/>
+      <c r="AB103" s="14"/>
+      <c r="AC103" s="14"/>
+      <c r="AD103" s="14"/>
+      <c r="AE103" s="14"/>
+      <c r="AF103" s="14"/>
+      <c r="AG103" s="14"/>
+      <c r="AH103" s="14"/>
+      <c r="AI103" s="14"/>
+      <c r="AJ103" s="14"/>
+      <c r="AK103" s="14"/>
+      <c r="AL103" s="14"/>
+      <c r="AM103" s="14"/>
+      <c r="AN103" s="14"/>
+      <c r="AO103" s="14"/>
+      <c r="AP103" s="14"/>
+      <c r="AQ103" s="14"/>
+      <c r="AR103" s="14"/>
+      <c r="AS103" s="14"/>
+      <c r="AT103" s="14"/>
+      <c r="AU103" s="14"/>
+      <c r="AV103" s="14"/>
+      <c r="AW103" s="14"/>
+      <c r="AX103" s="14"/>
+      <c r="AY103" s="14"/>
+      <c r="AZ103" s="14"/>
+      <c r="BA103" s="14"/>
+      <c r="BB103" s="14"/>
+      <c r="BC103" s="14"/>
+      <c r="BD103" s="14"/>
+      <c r="BE103" s="14"/>
+      <c r="BF103" s="14"/>
+      <c r="BG103" s="14"/>
+      <c r="BH103" s="14"/>
+      <c r="BI103" s="14"/>
+      <c r="BJ103" s="14"/>
+      <c r="BK103" s="14"/>
+      <c r="BL103" s="14"/>
+      <c r="BM103" s="14"/>
+      <c r="BN103" s="14"/>
+      <c r="BO103" s="14"/>
+      <c r="BP103" s="14"/>
+      <c r="BQ103" s="14"/>
+      <c r="BR103" s="14"/>
+      <c r="BS103" s="14"/>
+      <c r="BT103" s="14"/>
+      <c r="BU103" s="14"/>
+      <c r="BV103" s="14"/>
+      <c r="BW103" s="14"/>
+      <c r="BX103" s="14"/>
+      <c r="BY103" s="14"/>
+      <c r="BZ103" s="14"/>
+      <c r="CA103" s="14"/>
+      <c r="CB103" s="14"/>
+      <c r="CC103" s="14"/>
+      <c r="CD103" s="14"/>
+      <c r="CE103" s="14"/>
+      <c r="CF103" s="14"/>
+      <c r="CG103" s="14"/>
+      <c r="CH103" s="14"/>
+      <c r="CI103" s="14"/>
+      <c r="CJ103" s="14"/>
+      <c r="CK103" s="14"/>
+      <c r="CL103" s="14"/>
+      <c r="CM103" s="14"/>
+      <c r="CN103" s="14"/>
+      <c r="CO103" s="14"/>
+      <c r="CP103" s="14"/>
+      <c r="CQ103" s="14"/>
+      <c r="CR103" s="14"/>
+      <c r="CS103" s="14"/>
+      <c r="CT103" s="14"/>
+      <c r="CU103" s="14"/>
+      <c r="CV103" s="14"/>
+      <c r="CW103" s="14"/>
+      <c r="CX103" s="14"/>
+      <c r="CY103" s="14"/>
+      <c r="CZ103" s="14"/>
+      <c r="DA103" s="14"/>
+      <c r="DB103" s="14"/>
+      <c r="DC103" s="14"/>
+      <c r="DD103" s="14"/>
+      <c r="DE103" s="14"/>
+      <c r="DF103" s="14"/>
+      <c r="DG103" s="14"/>
+      <c r="DH103" s="14"/>
+      <c r="DI103" s="14"/>
+      <c r="DJ103" s="14"/>
+      <c r="DK103" s="14"/>
+      <c r="DL103" s="14"/>
+      <c r="DM103" s="14"/>
+      <c r="DN103" s="14"/>
+      <c r="DO103" s="14"/>
+      <c r="DP103" s="14"/>
+      <c r="DQ103" s="14"/>
+      <c r="DR103" s="14"/>
+      <c r="DS103" s="14"/>
+      <c r="DT103" s="14"/>
+      <c r="DU103" s="14"/>
+      <c r="DV103" s="14"/>
+      <c r="DW103" s="14"/>
+      <c r="DX103" s="14"/>
+      <c r="DY103" s="14"/>
+      <c r="DZ103" s="14"/>
+      <c r="EA103" s="14"/>
+      <c r="EB103" s="14"/>
+      <c r="EC103" s="14"/>
+      <c r="ED103" s="14"/>
+      <c r="EE103" s="14"/>
+      <c r="EF103" s="14"/>
+      <c r="EG103" s="14"/>
+      <c r="EH103" s="14"/>
+      <c r="EI103" s="14"/>
+      <c r="EJ103" s="14"/>
+      <c r="EK103" s="14"/>
+      <c r="EL103" s="14"/>
+      <c r="EM103" s="14"/>
+      <c r="EN103" s="14"/>
+      <c r="EO103" s="14"/>
+      <c r="EP103" s="14"/>
+      <c r="EQ103" s="14"/>
+      <c r="ER103" s="14"/>
+      <c r="ES103" s="14"/>
+      <c r="ET103" s="14"/>
+      <c r="EU103" s="14"/>
+      <c r="EV103" s="14"/>
+      <c r="EW103" s="14"/>
       <c r="EX103" s="44"/>
       <c r="EY103" s="44"/>
       <c r="EZ103" s="44"/>
@@ -23346,169 +23356,166 @@
       <c r="GK103" s="44"/>
     </row>
     <row r="104" spans="1:193" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
-      <c r="A104" s="17"/>
-      <c r="B104" s="74" t="s">
-        <v>141</v>
-      </c>
-      <c r="C104" s="83" t="s">
-        <v>27</v>
-      </c>
-      <c r="D104" s="37">
-        <v>0</v>
-      </c>
-      <c r="E104" s="84" t="s">
-        <v>27</v>
-      </c>
-      <c r="F104" s="84" t="s">
-        <v>27</v>
-      </c>
-      <c r="G104" s="9"/>
-      <c r="H104" s="9"/>
-      <c r="I104" s="47"/>
-      <c r="J104" s="48"/>
-      <c r="K104" s="48"/>
-      <c r="L104" s="48"/>
-      <c r="M104" s="49"/>
-      <c r="N104" s="39"/>
-      <c r="O104" s="39"/>
-      <c r="P104" s="56"/>
-      <c r="Q104" s="57"/>
-      <c r="R104" s="57"/>
-      <c r="S104" s="57"/>
-      <c r="T104" s="58"/>
-      <c r="U104" s="39"/>
-      <c r="V104" s="39"/>
-      <c r="W104" s="47"/>
-      <c r="X104" s="48"/>
-      <c r="Y104" s="48"/>
-      <c r="Z104" s="48"/>
-      <c r="AA104" s="49"/>
-      <c r="AB104" s="39"/>
-      <c r="AC104" s="39"/>
-      <c r="AD104" s="56"/>
-      <c r="AE104" s="57"/>
-      <c r="AF104" s="57"/>
-      <c r="AG104" s="57"/>
-      <c r="AH104" s="58"/>
-      <c r="AI104" s="39"/>
-      <c r="AJ104" s="39"/>
-      <c r="AK104" s="47"/>
-      <c r="AL104" s="48"/>
-      <c r="AM104" s="48"/>
-      <c r="AN104" s="48"/>
-      <c r="AO104" s="49"/>
-      <c r="AP104" s="39"/>
-      <c r="AQ104" s="39"/>
-      <c r="AR104" s="56"/>
-      <c r="AS104" s="57"/>
-      <c r="AT104" s="57"/>
-      <c r="AU104" s="57"/>
-      <c r="AV104" s="58"/>
-      <c r="AW104" s="39"/>
-      <c r="AX104" s="39"/>
-      <c r="AY104" s="47"/>
-      <c r="AZ104" s="48"/>
-      <c r="BA104" s="48"/>
-      <c r="BB104" s="48"/>
-      <c r="BC104" s="49"/>
-      <c r="BD104" s="39"/>
-      <c r="BE104" s="39"/>
-      <c r="BF104" s="56"/>
-      <c r="BG104" s="57"/>
-      <c r="BH104" s="57"/>
-      <c r="BI104" s="57"/>
-      <c r="BJ104" s="58"/>
-      <c r="BK104" s="39"/>
-      <c r="BL104" s="39"/>
-      <c r="BM104" s="47"/>
-      <c r="BN104" s="48"/>
-      <c r="BO104" s="48"/>
-      <c r="BP104" s="48"/>
-      <c r="BQ104" s="49"/>
-      <c r="BR104" s="39"/>
-      <c r="BS104" s="39"/>
-      <c r="BT104" s="47"/>
-      <c r="BU104" s="48"/>
-      <c r="BV104" s="48"/>
-      <c r="BW104" s="48"/>
-      <c r="BX104" s="49"/>
-      <c r="BY104" s="39"/>
-      <c r="BZ104" s="39"/>
-      <c r="CA104" s="56"/>
-      <c r="CB104" s="57"/>
-      <c r="CC104" s="57"/>
-      <c r="CD104" s="57"/>
-      <c r="CE104" s="58"/>
-      <c r="CF104" s="39"/>
-      <c r="CG104" s="39"/>
-      <c r="CH104" s="47"/>
-      <c r="CI104" s="48"/>
-      <c r="CJ104" s="48"/>
-      <c r="CK104" s="48"/>
-      <c r="CL104" s="49"/>
-      <c r="CM104" s="39"/>
-      <c r="CN104" s="39"/>
-      <c r="CO104" s="56"/>
-      <c r="CP104" s="57"/>
-      <c r="CQ104" s="57"/>
-      <c r="CR104" s="57"/>
-      <c r="CS104" s="58"/>
-      <c r="CT104" s="39"/>
-      <c r="CU104" s="39"/>
-      <c r="CV104" s="47"/>
-      <c r="CW104" s="48"/>
-      <c r="CX104" s="48"/>
-      <c r="CY104" s="48"/>
-      <c r="CZ104" s="49"/>
-      <c r="DA104" s="39"/>
-      <c r="DB104" s="39"/>
-      <c r="DC104" s="56"/>
-      <c r="DD104" s="57"/>
-      <c r="DE104" s="57"/>
-      <c r="DF104" s="57"/>
-      <c r="DG104" s="58"/>
-      <c r="DH104" s="39"/>
-      <c r="DI104" s="39"/>
-      <c r="DJ104" s="47"/>
-      <c r="DK104" s="48"/>
-      <c r="DL104" s="48"/>
-      <c r="DM104" s="48"/>
-      <c r="DN104" s="49"/>
-      <c r="DO104" s="39"/>
-      <c r="DP104" s="39"/>
-      <c r="DQ104" s="56"/>
-      <c r="DR104" s="57"/>
-      <c r="DS104" s="57"/>
-      <c r="DT104" s="57"/>
-      <c r="DU104" s="58"/>
-      <c r="DV104" s="39"/>
-      <c r="DW104" s="39"/>
-      <c r="DX104" s="47"/>
-      <c r="DY104" s="48"/>
-      <c r="DZ104" s="48"/>
-      <c r="EA104" s="48"/>
-      <c r="EB104" s="49"/>
-      <c r="EC104" s="39"/>
-      <c r="ED104" s="39"/>
-      <c r="EE104" s="56"/>
-      <c r="EF104" s="57"/>
-      <c r="EG104" s="57"/>
-      <c r="EH104" s="57"/>
-      <c r="EI104" s="58"/>
-      <c r="EJ104" s="39"/>
-      <c r="EK104" s="39"/>
-      <c r="EL104" s="47"/>
-      <c r="EM104" s="48"/>
-      <c r="EN104" s="48"/>
-      <c r="EO104" s="48"/>
-      <c r="EP104" s="49"/>
-      <c r="EQ104" s="39"/>
-      <c r="ER104" s="39"/>
-      <c r="ES104" s="47"/>
-      <c r="ET104" s="48"/>
-      <c r="EU104" s="48"/>
-      <c r="EV104" s="48"/>
-      <c r="EW104" s="49"/>
+      <c r="A104" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="B104" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C104" s="11"/>
+      <c r="D104" s="12"/>
+      <c r="E104" s="24"/>
+      <c r="F104" s="25"/>
+      <c r="G104" s="13"/>
+      <c r="H104" s="13" t="str">
+        <f t="shared" si="71"/>
+        <v/>
+      </c>
+      <c r="I104" s="15"/>
+      <c r="J104" s="15"/>
+      <c r="K104" s="15"/>
+      <c r="L104" s="15"/>
+      <c r="M104" s="15"/>
+      <c r="N104" s="15"/>
+      <c r="O104" s="15"/>
+      <c r="P104" s="15"/>
+      <c r="Q104" s="15"/>
+      <c r="R104" s="15"/>
+      <c r="S104" s="15"/>
+      <c r="T104" s="15"/>
+      <c r="U104" s="15"/>
+      <c r="V104" s="15"/>
+      <c r="W104" s="15"/>
+      <c r="X104" s="15"/>
+      <c r="Y104" s="15"/>
+      <c r="Z104" s="15"/>
+      <c r="AA104" s="15"/>
+      <c r="AB104" s="15"/>
+      <c r="AC104" s="15"/>
+      <c r="AD104" s="15"/>
+      <c r="AE104" s="15"/>
+      <c r="AF104" s="15"/>
+      <c r="AG104" s="15"/>
+      <c r="AH104" s="15"/>
+      <c r="AI104" s="15"/>
+      <c r="AJ104" s="15"/>
+      <c r="AK104" s="15"/>
+      <c r="AL104" s="15"/>
+      <c r="AM104" s="15"/>
+      <c r="AN104" s="15"/>
+      <c r="AO104" s="15"/>
+      <c r="AP104" s="15"/>
+      <c r="AQ104" s="15"/>
+      <c r="AR104" s="15"/>
+      <c r="AS104" s="15"/>
+      <c r="AT104" s="15"/>
+      <c r="AU104" s="15"/>
+      <c r="AV104" s="15"/>
+      <c r="AW104" s="15"/>
+      <c r="AX104" s="15"/>
+      <c r="AY104" s="15"/>
+      <c r="AZ104" s="15"/>
+      <c r="BA104" s="15"/>
+      <c r="BB104" s="15"/>
+      <c r="BC104" s="15"/>
+      <c r="BD104" s="15"/>
+      <c r="BE104" s="15"/>
+      <c r="BF104" s="15"/>
+      <c r="BG104" s="15"/>
+      <c r="BH104" s="15"/>
+      <c r="BI104" s="15"/>
+      <c r="BJ104" s="15"/>
+      <c r="BK104" s="15"/>
+      <c r="BL104" s="15"/>
+      <c r="BM104" s="15"/>
+      <c r="BN104" s="15"/>
+      <c r="BO104" s="15"/>
+      <c r="BP104" s="15"/>
+      <c r="BQ104" s="15"/>
+      <c r="BR104" s="15"/>
+      <c r="BS104" s="15"/>
+      <c r="BT104" s="15"/>
+      <c r="BU104" s="15"/>
+      <c r="BV104" s="15"/>
+      <c r="BW104" s="15"/>
+      <c r="BX104" s="15"/>
+      <c r="BY104" s="15"/>
+      <c r="BZ104" s="15"/>
+      <c r="CA104" s="15"/>
+      <c r="CB104" s="15"/>
+      <c r="CC104" s="15"/>
+      <c r="CD104" s="15"/>
+      <c r="CE104" s="15"/>
+      <c r="CF104" s="15"/>
+      <c r="CG104" s="15"/>
+      <c r="CH104" s="15"/>
+      <c r="CI104" s="15"/>
+      <c r="CJ104" s="15"/>
+      <c r="CK104" s="15"/>
+      <c r="CL104" s="15"/>
+      <c r="CM104" s="15"/>
+      <c r="CN104" s="15"/>
+      <c r="CO104" s="15"/>
+      <c r="CP104" s="15"/>
+      <c r="CQ104" s="15"/>
+      <c r="CR104" s="15"/>
+      <c r="CS104" s="15"/>
+      <c r="CT104" s="15"/>
+      <c r="CU104" s="15"/>
+      <c r="CV104" s="15"/>
+      <c r="CW104" s="15"/>
+      <c r="CX104" s="15"/>
+      <c r="CY104" s="15"/>
+      <c r="CZ104" s="15"/>
+      <c r="DA104" s="15"/>
+      <c r="DB104" s="15"/>
+      <c r="DC104" s="15"/>
+      <c r="DD104" s="15"/>
+      <c r="DE104" s="15"/>
+      <c r="DF104" s="15"/>
+      <c r="DG104" s="15"/>
+      <c r="DH104" s="15"/>
+      <c r="DI104" s="15"/>
+      <c r="DJ104" s="15"/>
+      <c r="DK104" s="15"/>
+      <c r="DL104" s="15"/>
+      <c r="DM104" s="15"/>
+      <c r="DN104" s="15"/>
+      <c r="DO104" s="15"/>
+      <c r="DP104" s="15"/>
+      <c r="DQ104" s="15"/>
+      <c r="DR104" s="15"/>
+      <c r="DS104" s="15"/>
+      <c r="DT104" s="15"/>
+      <c r="DU104" s="15"/>
+      <c r="DV104" s="15"/>
+      <c r="DW104" s="15"/>
+      <c r="DX104" s="15"/>
+      <c r="DY104" s="15"/>
+      <c r="DZ104" s="15"/>
+      <c r="EA104" s="15"/>
+      <c r="EB104" s="15"/>
+      <c r="EC104" s="15"/>
+      <c r="ED104" s="15"/>
+      <c r="EE104" s="15"/>
+      <c r="EF104" s="15"/>
+      <c r="EG104" s="15"/>
+      <c r="EH104" s="15"/>
+      <c r="EI104" s="15"/>
+      <c r="EJ104" s="15"/>
+      <c r="EK104" s="15"/>
+      <c r="EL104" s="15"/>
+      <c r="EM104" s="15"/>
+      <c r="EN104" s="15"/>
+      <c r="EO104" s="15"/>
+      <c r="EP104" s="15"/>
+      <c r="EQ104" s="15"/>
+      <c r="ER104" s="15"/>
+      <c r="ES104" s="15"/>
+      <c r="ET104" s="15"/>
+      <c r="EU104" s="15"/>
+      <c r="EV104" s="15"/>
+      <c r="EW104" s="15"/>
       <c r="EX104" s="44"/>
       <c r="EY104" s="44"/>
       <c r="EZ104" s="44"/>
@@ -23550,630 +23557,23 @@
       <c r="GJ104" s="44"/>
       <c r="GK104" s="44"/>
     </row>
-    <row r="105" spans="1:193" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
-      <c r="A105" s="17"/>
-      <c r="B105" s="74" t="s">
-        <v>142</v>
-      </c>
-      <c r="C105" s="83" t="s">
-        <v>27</v>
-      </c>
-      <c r="D105" s="37">
-        <v>0</v>
-      </c>
-      <c r="E105" s="84" t="s">
-        <v>27</v>
-      </c>
-      <c r="F105" s="84" t="s">
-        <v>27</v>
-      </c>
-      <c r="G105" s="9"/>
-      <c r="H105" s="9"/>
-      <c r="I105" s="47"/>
-      <c r="J105" s="48"/>
-      <c r="K105" s="48"/>
-      <c r="L105" s="48"/>
-      <c r="M105" s="49"/>
-      <c r="N105" s="39"/>
-      <c r="O105" s="39"/>
-      <c r="P105" s="56"/>
-      <c r="Q105" s="57"/>
-      <c r="R105" s="57"/>
-      <c r="S105" s="57"/>
-      <c r="T105" s="58"/>
-      <c r="U105" s="39"/>
-      <c r="V105" s="39"/>
-      <c r="W105" s="47"/>
-      <c r="X105" s="48"/>
-      <c r="Y105" s="48"/>
-      <c r="Z105" s="48"/>
-      <c r="AA105" s="49"/>
-      <c r="AB105" s="39"/>
-      <c r="AC105" s="39"/>
-      <c r="AD105" s="56"/>
-      <c r="AE105" s="57"/>
-      <c r="AF105" s="57"/>
-      <c r="AG105" s="57"/>
-      <c r="AH105" s="58"/>
-      <c r="AI105" s="39"/>
-      <c r="AJ105" s="39"/>
-      <c r="AK105" s="47"/>
-      <c r="AL105" s="48"/>
-      <c r="AM105" s="48"/>
-      <c r="AN105" s="48"/>
-      <c r="AO105" s="49"/>
-      <c r="AP105" s="39"/>
-      <c r="AQ105" s="39"/>
-      <c r="AR105" s="56"/>
-      <c r="AS105" s="57"/>
-      <c r="AT105" s="57"/>
-      <c r="AU105" s="57"/>
-      <c r="AV105" s="58"/>
-      <c r="AW105" s="39"/>
-      <c r="AX105" s="39"/>
-      <c r="AY105" s="47"/>
-      <c r="AZ105" s="48"/>
-      <c r="BA105" s="48"/>
-      <c r="BB105" s="48"/>
-      <c r="BC105" s="49"/>
-      <c r="BD105" s="39"/>
-      <c r="BE105" s="39"/>
-      <c r="BF105" s="56"/>
-      <c r="BG105" s="57"/>
-      <c r="BH105" s="57"/>
-      <c r="BI105" s="57"/>
-      <c r="BJ105" s="58"/>
-      <c r="BK105" s="39"/>
-      <c r="BL105" s="39"/>
-      <c r="BM105" s="47"/>
-      <c r="BN105" s="48"/>
-      <c r="BO105" s="48"/>
-      <c r="BP105" s="48"/>
-      <c r="BQ105" s="49"/>
-      <c r="BR105" s="39"/>
-      <c r="BS105" s="39"/>
-      <c r="BT105" s="47"/>
-      <c r="BU105" s="48"/>
-      <c r="BV105" s="48"/>
-      <c r="BW105" s="48"/>
-      <c r="BX105" s="49"/>
-      <c r="BY105" s="39"/>
-      <c r="BZ105" s="39"/>
-      <c r="CA105" s="56"/>
-      <c r="CB105" s="57"/>
-      <c r="CC105" s="57"/>
-      <c r="CD105" s="57"/>
-      <c r="CE105" s="58"/>
-      <c r="CF105" s="39"/>
-      <c r="CG105" s="39"/>
-      <c r="CH105" s="47"/>
-      <c r="CI105" s="48"/>
-      <c r="CJ105" s="48"/>
-      <c r="CK105" s="48"/>
-      <c r="CL105" s="49"/>
-      <c r="CM105" s="39"/>
-      <c r="CN105" s="39"/>
-      <c r="CO105" s="56"/>
-      <c r="CP105" s="57"/>
-      <c r="CQ105" s="57"/>
-      <c r="CR105" s="57"/>
-      <c r="CS105" s="58"/>
-      <c r="CT105" s="39"/>
-      <c r="CU105" s="39"/>
-      <c r="CV105" s="47"/>
-      <c r="CW105" s="48"/>
-      <c r="CX105" s="48"/>
-      <c r="CY105" s="48"/>
-      <c r="CZ105" s="49"/>
-      <c r="DA105" s="39"/>
-      <c r="DB105" s="39"/>
-      <c r="DC105" s="56"/>
-      <c r="DD105" s="57"/>
-      <c r="DE105" s="57"/>
-      <c r="DF105" s="57"/>
-      <c r="DG105" s="58"/>
-      <c r="DH105" s="39"/>
-      <c r="DI105" s="39"/>
-      <c r="DJ105" s="47"/>
-      <c r="DK105" s="48"/>
-      <c r="DL105" s="48"/>
-      <c r="DM105" s="48"/>
-      <c r="DN105" s="49"/>
-      <c r="DO105" s="39"/>
-      <c r="DP105" s="39"/>
-      <c r="DQ105" s="56"/>
-      <c r="DR105" s="57"/>
-      <c r="DS105" s="57"/>
-      <c r="DT105" s="57"/>
-      <c r="DU105" s="58"/>
-      <c r="DV105" s="39"/>
-      <c r="DW105" s="39"/>
-      <c r="DX105" s="47"/>
-      <c r="DY105" s="48"/>
-      <c r="DZ105" s="48"/>
-      <c r="EA105" s="48"/>
-      <c r="EB105" s="49"/>
-      <c r="EC105" s="39"/>
-      <c r="ED105" s="39"/>
-      <c r="EE105" s="56"/>
-      <c r="EF105" s="57"/>
-      <c r="EG105" s="57"/>
-      <c r="EH105" s="57"/>
-      <c r="EI105" s="58"/>
-      <c r="EJ105" s="39"/>
-      <c r="EK105" s="39"/>
-      <c r="EL105" s="47"/>
-      <c r="EM105" s="48"/>
-      <c r="EN105" s="48"/>
-      <c r="EO105" s="48"/>
-      <c r="EP105" s="49"/>
-      <c r="EQ105" s="39"/>
-      <c r="ER105" s="39"/>
-      <c r="ES105" s="47"/>
-      <c r="ET105" s="48"/>
-      <c r="EU105" s="48"/>
-      <c r="EV105" s="48"/>
-      <c r="EW105" s="49"/>
-      <c r="EX105" s="44"/>
-      <c r="EY105" s="44"/>
-      <c r="EZ105" s="44"/>
-      <c r="FA105" s="44"/>
-      <c r="FB105" s="44"/>
-      <c r="FC105" s="44"/>
-      <c r="FD105" s="44"/>
-      <c r="FE105" s="44"/>
-      <c r="FF105" s="44"/>
-      <c r="FG105" s="44"/>
-      <c r="FH105" s="44"/>
-      <c r="FI105" s="44"/>
-      <c r="FJ105" s="44"/>
-      <c r="FK105" s="44"/>
-      <c r="FL105" s="44"/>
-      <c r="FM105" s="44"/>
-      <c r="FN105" s="44"/>
-      <c r="FO105" s="44"/>
-      <c r="FP105" s="44"/>
-      <c r="FQ105" s="44"/>
-      <c r="FR105" s="44"/>
-      <c r="FS105" s="44"/>
-      <c r="FT105" s="44"/>
-      <c r="FU105" s="44"/>
-      <c r="FV105" s="44"/>
-      <c r="FW105" s="44"/>
-      <c r="FX105" s="44"/>
-      <c r="FY105" s="44"/>
-      <c r="FZ105" s="44"/>
-      <c r="GA105" s="44"/>
-      <c r="GB105" s="44"/>
-      <c r="GC105" s="44"/>
-      <c r="GD105" s="44"/>
-      <c r="GE105" s="44"/>
-      <c r="GF105" s="44"/>
-      <c r="GG105" s="44"/>
-      <c r="GH105" s="44"/>
-      <c r="GI105" s="44"/>
-      <c r="GJ105" s="44"/>
-      <c r="GK105" s="44"/>
+    <row r="105" spans="1:193" ht="30" customHeight="1">
+      <c r="G105" s="3"/>
     </row>
-    <row r="106" spans="1:193" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
-      <c r="A106" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="B106" s="21"/>
-      <c r="C106" s="20"/>
-      <c r="D106" s="8"/>
-      <c r="E106" s="23"/>
-      <c r="F106" s="23"/>
-      <c r="G106" s="9"/>
-      <c r="H106" s="9" t="str">
-        <f t="shared" si="71"/>
-        <v/>
-      </c>
-      <c r="I106" s="14"/>
-      <c r="J106" s="14"/>
-      <c r="K106" s="14"/>
-      <c r="L106" s="14"/>
-      <c r="M106" s="14"/>
-      <c r="N106" s="14"/>
-      <c r="O106" s="14"/>
-      <c r="P106" s="14"/>
-      <c r="Q106" s="14"/>
-      <c r="R106" s="14"/>
-      <c r="S106" s="14"/>
-      <c r="T106" s="14"/>
-      <c r="U106" s="14"/>
-      <c r="V106" s="14"/>
-      <c r="W106" s="14"/>
-      <c r="X106" s="14"/>
-      <c r="Y106" s="14"/>
-      <c r="Z106" s="14"/>
-      <c r="AA106" s="14"/>
-      <c r="AB106" s="14"/>
-      <c r="AC106" s="14"/>
-      <c r="AD106" s="14"/>
-      <c r="AE106" s="14"/>
-      <c r="AF106" s="14"/>
-      <c r="AG106" s="14"/>
-      <c r="AH106" s="14"/>
-      <c r="AI106" s="14"/>
-      <c r="AJ106" s="14"/>
-      <c r="AK106" s="14"/>
-      <c r="AL106" s="14"/>
-      <c r="AM106" s="14"/>
-      <c r="AN106" s="14"/>
-      <c r="AO106" s="14"/>
-      <c r="AP106" s="14"/>
-      <c r="AQ106" s="14"/>
-      <c r="AR106" s="14"/>
-      <c r="AS106" s="14"/>
-      <c r="AT106" s="14"/>
-      <c r="AU106" s="14"/>
-      <c r="AV106" s="14"/>
-      <c r="AW106" s="14"/>
-      <c r="AX106" s="14"/>
-      <c r="AY106" s="14"/>
-      <c r="AZ106" s="14"/>
-      <c r="BA106" s="14"/>
-      <c r="BB106" s="14"/>
-      <c r="BC106" s="14"/>
-      <c r="BD106" s="14"/>
-      <c r="BE106" s="14"/>
-      <c r="BF106" s="14"/>
-      <c r="BG106" s="14"/>
-      <c r="BH106" s="14"/>
-      <c r="BI106" s="14"/>
-      <c r="BJ106" s="14"/>
-      <c r="BK106" s="14"/>
-      <c r="BL106" s="14"/>
-      <c r="BM106" s="14"/>
-      <c r="BN106" s="14"/>
-      <c r="BO106" s="14"/>
-      <c r="BP106" s="14"/>
-      <c r="BQ106" s="14"/>
-      <c r="BR106" s="14"/>
-      <c r="BS106" s="14"/>
-      <c r="BT106" s="14"/>
-      <c r="BU106" s="14"/>
-      <c r="BV106" s="14"/>
-      <c r="BW106" s="14"/>
-      <c r="BX106" s="14"/>
-      <c r="BY106" s="14"/>
-      <c r="BZ106" s="14"/>
-      <c r="CA106" s="14"/>
-      <c r="CB106" s="14"/>
-      <c r="CC106" s="14"/>
-      <c r="CD106" s="14"/>
-      <c r="CE106" s="14"/>
-      <c r="CF106" s="14"/>
-      <c r="CG106" s="14"/>
-      <c r="CH106" s="14"/>
-      <c r="CI106" s="14"/>
-      <c r="CJ106" s="14"/>
-      <c r="CK106" s="14"/>
-      <c r="CL106" s="14"/>
-      <c r="CM106" s="14"/>
-      <c r="CN106" s="14"/>
-      <c r="CO106" s="14"/>
-      <c r="CP106" s="14"/>
-      <c r="CQ106" s="14"/>
-      <c r="CR106" s="14"/>
-      <c r="CS106" s="14"/>
-      <c r="CT106" s="14"/>
-      <c r="CU106" s="14"/>
-      <c r="CV106" s="14"/>
-      <c r="CW106" s="14"/>
-      <c r="CX106" s="14"/>
-      <c r="CY106" s="14"/>
-      <c r="CZ106" s="14"/>
-      <c r="DA106" s="14"/>
-      <c r="DB106" s="14"/>
-      <c r="DC106" s="14"/>
-      <c r="DD106" s="14"/>
-      <c r="DE106" s="14"/>
-      <c r="DF106" s="14"/>
-      <c r="DG106" s="14"/>
-      <c r="DH106" s="14"/>
-      <c r="DI106" s="14"/>
-      <c r="DJ106" s="14"/>
-      <c r="DK106" s="14"/>
-      <c r="DL106" s="14"/>
-      <c r="DM106" s="14"/>
-      <c r="DN106" s="14"/>
-      <c r="DO106" s="14"/>
-      <c r="DP106" s="14"/>
-      <c r="DQ106" s="14"/>
-      <c r="DR106" s="14"/>
-      <c r="DS106" s="14"/>
-      <c r="DT106" s="14"/>
-      <c r="DU106" s="14"/>
-      <c r="DV106" s="14"/>
-      <c r="DW106" s="14"/>
-      <c r="DX106" s="14"/>
-      <c r="DY106" s="14"/>
-      <c r="DZ106" s="14"/>
-      <c r="EA106" s="14"/>
-      <c r="EB106" s="14"/>
-      <c r="EC106" s="14"/>
-      <c r="ED106" s="14"/>
-      <c r="EE106" s="14"/>
-      <c r="EF106" s="14"/>
-      <c r="EG106" s="14"/>
-      <c r="EH106" s="14"/>
-      <c r="EI106" s="14"/>
-      <c r="EJ106" s="14"/>
-      <c r="EK106" s="14"/>
-      <c r="EL106" s="14"/>
-      <c r="EM106" s="14"/>
-      <c r="EN106" s="14"/>
-      <c r="EO106" s="14"/>
-      <c r="EP106" s="14"/>
-      <c r="EQ106" s="14"/>
-      <c r="ER106" s="14"/>
-      <c r="ES106" s="14"/>
-      <c r="ET106" s="14"/>
-      <c r="EU106" s="14"/>
-      <c r="EV106" s="14"/>
-      <c r="EW106" s="14"/>
-      <c r="EX106" s="44"/>
-      <c r="EY106" s="44"/>
-      <c r="EZ106" s="44"/>
-      <c r="FA106" s="44"/>
-      <c r="FB106" s="44"/>
-      <c r="FC106" s="44"/>
-      <c r="FD106" s="44"/>
-      <c r="FE106" s="44"/>
-      <c r="FF106" s="44"/>
-      <c r="FG106" s="44"/>
-      <c r="FH106" s="44"/>
-      <c r="FI106" s="44"/>
-      <c r="FJ106" s="44"/>
-      <c r="FK106" s="44"/>
-      <c r="FL106" s="44"/>
-      <c r="FM106" s="44"/>
-      <c r="FN106" s="44"/>
-      <c r="FO106" s="44"/>
-      <c r="FP106" s="44"/>
-      <c r="FQ106" s="44"/>
-      <c r="FR106" s="44"/>
-      <c r="FS106" s="44"/>
-      <c r="FT106" s="44"/>
-      <c r="FU106" s="44"/>
-      <c r="FV106" s="44"/>
-      <c r="FW106" s="44"/>
-      <c r="FX106" s="44"/>
-      <c r="FY106" s="44"/>
-      <c r="FZ106" s="44"/>
-      <c r="GA106" s="44"/>
-      <c r="GB106" s="44"/>
-      <c r="GC106" s="44"/>
-      <c r="GD106" s="44"/>
-      <c r="GE106" s="44"/>
-      <c r="GF106" s="44"/>
-      <c r="GG106" s="44"/>
-      <c r="GH106" s="44"/>
-      <c r="GI106" s="44"/>
-      <c r="GJ106" s="44"/>
-      <c r="GK106" s="44"/>
+    <row r="106" spans="1:193" ht="30" customHeight="1">
+      <c r="C106" s="6"/>
+      <c r="F106" s="18"/>
     </row>
-    <row r="107" spans="1:193" s="1" customFormat="1" ht="30" customHeight="1" thickBot="1">
-      <c r="A107" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="B107" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C107" s="11"/>
-      <c r="D107" s="12"/>
-      <c r="E107" s="24"/>
-      <c r="F107" s="25"/>
-      <c r="G107" s="13"/>
-      <c r="H107" s="13" t="str">
-        <f t="shared" si="71"/>
-        <v/>
-      </c>
-      <c r="I107" s="15"/>
-      <c r="J107" s="15"/>
-      <c r="K107" s="15"/>
-      <c r="L107" s="15"/>
-      <c r="M107" s="15"/>
-      <c r="N107" s="15"/>
-      <c r="O107" s="15"/>
-      <c r="P107" s="15"/>
-      <c r="Q107" s="15"/>
-      <c r="R107" s="15"/>
-      <c r="S107" s="15"/>
-      <c r="T107" s="15"/>
-      <c r="U107" s="15"/>
-      <c r="V107" s="15"/>
-      <c r="W107" s="15"/>
-      <c r="X107" s="15"/>
-      <c r="Y107" s="15"/>
-      <c r="Z107" s="15"/>
-      <c r="AA107" s="15"/>
-      <c r="AB107" s="15"/>
-      <c r="AC107" s="15"/>
-      <c r="AD107" s="15"/>
-      <c r="AE107" s="15"/>
-      <c r="AF107" s="15"/>
-      <c r="AG107" s="15"/>
-      <c r="AH107" s="15"/>
-      <c r="AI107" s="15"/>
-      <c r="AJ107" s="15"/>
-      <c r="AK107" s="15"/>
-      <c r="AL107" s="15"/>
-      <c r="AM107" s="15"/>
-      <c r="AN107" s="15"/>
-      <c r="AO107" s="15"/>
-      <c r="AP107" s="15"/>
-      <c r="AQ107" s="15"/>
-      <c r="AR107" s="15"/>
-      <c r="AS107" s="15"/>
-      <c r="AT107" s="15"/>
-      <c r="AU107" s="15"/>
-      <c r="AV107" s="15"/>
-      <c r="AW107" s="15"/>
-      <c r="AX107" s="15"/>
-      <c r="AY107" s="15"/>
-      <c r="AZ107" s="15"/>
-      <c r="BA107" s="15"/>
-      <c r="BB107" s="15"/>
-      <c r="BC107" s="15"/>
-      <c r="BD107" s="15"/>
-      <c r="BE107" s="15"/>
-      <c r="BF107" s="15"/>
-      <c r="BG107" s="15"/>
-      <c r="BH107" s="15"/>
-      <c r="BI107" s="15"/>
-      <c r="BJ107" s="15"/>
-      <c r="BK107" s="15"/>
-      <c r="BL107" s="15"/>
-      <c r="BM107" s="15"/>
-      <c r="BN107" s="15"/>
-      <c r="BO107" s="15"/>
-      <c r="BP107" s="15"/>
-      <c r="BQ107" s="15"/>
-      <c r="BR107" s="15"/>
-      <c r="BS107" s="15"/>
-      <c r="BT107" s="15"/>
-      <c r="BU107" s="15"/>
-      <c r="BV107" s="15"/>
-      <c r="BW107" s="15"/>
-      <c r="BX107" s="15"/>
-      <c r="BY107" s="15"/>
-      <c r="BZ107" s="15"/>
-      <c r="CA107" s="15"/>
-      <c r="CB107" s="15"/>
-      <c r="CC107" s="15"/>
-      <c r="CD107" s="15"/>
-      <c r="CE107" s="15"/>
-      <c r="CF107" s="15"/>
-      <c r="CG107" s="15"/>
-      <c r="CH107" s="15"/>
-      <c r="CI107" s="15"/>
-      <c r="CJ107" s="15"/>
-      <c r="CK107" s="15"/>
-      <c r="CL107" s="15"/>
-      <c r="CM107" s="15"/>
-      <c r="CN107" s="15"/>
-      <c r="CO107" s="15"/>
-      <c r="CP107" s="15"/>
-      <c r="CQ107" s="15"/>
-      <c r="CR107" s="15"/>
-      <c r="CS107" s="15"/>
-      <c r="CT107" s="15"/>
-      <c r="CU107" s="15"/>
-      <c r="CV107" s="15"/>
-      <c r="CW107" s="15"/>
-      <c r="CX107" s="15"/>
-      <c r="CY107" s="15"/>
-      <c r="CZ107" s="15"/>
-      <c r="DA107" s="15"/>
-      <c r="DB107" s="15"/>
-      <c r="DC107" s="15"/>
-      <c r="DD107" s="15"/>
-      <c r="DE107" s="15"/>
-      <c r="DF107" s="15"/>
-      <c r="DG107" s="15"/>
-      <c r="DH107" s="15"/>
-      <c r="DI107" s="15"/>
-      <c r="DJ107" s="15"/>
-      <c r="DK107" s="15"/>
-      <c r="DL107" s="15"/>
-      <c r="DM107" s="15"/>
-      <c r="DN107" s="15"/>
-      <c r="DO107" s="15"/>
-      <c r="DP107" s="15"/>
-      <c r="DQ107" s="15"/>
-      <c r="DR107" s="15"/>
-      <c r="DS107" s="15"/>
-      <c r="DT107" s="15"/>
-      <c r="DU107" s="15"/>
-      <c r="DV107" s="15"/>
-      <c r="DW107" s="15"/>
-      <c r="DX107" s="15"/>
-      <c r="DY107" s="15"/>
-      <c r="DZ107" s="15"/>
-      <c r="EA107" s="15"/>
-      <c r="EB107" s="15"/>
-      <c r="EC107" s="15"/>
-      <c r="ED107" s="15"/>
-      <c r="EE107" s="15"/>
-      <c r="EF107" s="15"/>
-      <c r="EG107" s="15"/>
-      <c r="EH107" s="15"/>
-      <c r="EI107" s="15"/>
-      <c r="EJ107" s="15"/>
-      <c r="EK107" s="15"/>
-      <c r="EL107" s="15"/>
-      <c r="EM107" s="15"/>
-      <c r="EN107" s="15"/>
-      <c r="EO107" s="15"/>
-      <c r="EP107" s="15"/>
-      <c r="EQ107" s="15"/>
-      <c r="ER107" s="15"/>
-      <c r="ES107" s="15"/>
-      <c r="ET107" s="15"/>
-      <c r="EU107" s="15"/>
-      <c r="EV107" s="15"/>
-      <c r="EW107" s="15"/>
-      <c r="EX107" s="44"/>
-      <c r="EY107" s="44"/>
-      <c r="EZ107" s="44"/>
-      <c r="FA107" s="44"/>
-      <c r="FB107" s="44"/>
-      <c r="FC107" s="44"/>
-      <c r="FD107" s="44"/>
-      <c r="FE107" s="44"/>
-      <c r="FF107" s="44"/>
-      <c r="FG107" s="44"/>
-      <c r="FH107" s="44"/>
-      <c r="FI107" s="44"/>
-      <c r="FJ107" s="44"/>
-      <c r="FK107" s="44"/>
-      <c r="FL107" s="44"/>
-      <c r="FM107" s="44"/>
-      <c r="FN107" s="44"/>
-      <c r="FO107" s="44"/>
-      <c r="FP107" s="44"/>
-      <c r="FQ107" s="44"/>
-      <c r="FR107" s="44"/>
-      <c r="FS107" s="44"/>
-      <c r="FT107" s="44"/>
-      <c r="FU107" s="44"/>
-      <c r="FV107" s="44"/>
-      <c r="FW107" s="44"/>
-      <c r="FX107" s="44"/>
-      <c r="FY107" s="44"/>
-      <c r="FZ107" s="44"/>
-      <c r="GA107" s="44"/>
-      <c r="GB107" s="44"/>
-      <c r="GC107" s="44"/>
-      <c r="GD107" s="44"/>
-      <c r="GE107" s="44"/>
-      <c r="GF107" s="44"/>
-      <c r="GG107" s="44"/>
-      <c r="GH107" s="44"/>
-      <c r="GI107" s="44"/>
-      <c r="GJ107" s="44"/>
-      <c r="GK107" s="44"/>
-    </row>
-    <row r="108" spans="1:193" ht="30" customHeight="1">
-      <c r="G108" s="3"/>
-    </row>
-    <row r="109" spans="1:193" ht="30" customHeight="1">
-      <c r="C109" s="6"/>
-      <c r="F109" s="18"/>
-    </row>
-    <row r="110" spans="1:193" ht="30" customHeight="1">
-      <c r="C110" s="7"/>
+    <row r="107" spans="1:193" ht="30" customHeight="1">
+      <c r="C107" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="219">
-    <mergeCell ref="BT48:BX48"/>
-    <mergeCell ref="AK47:AO47"/>
-    <mergeCell ref="AR48:AV48"/>
-    <mergeCell ref="AR47:AV47"/>
-    <mergeCell ref="AK48:AO48"/>
+    <mergeCell ref="BT43:BX43"/>
+    <mergeCell ref="AK42:AO42"/>
+    <mergeCell ref="AR43:AV43"/>
+    <mergeCell ref="AR42:AV42"/>
+    <mergeCell ref="AK43:AO43"/>
     <mergeCell ref="BF11:BJ11"/>
     <mergeCell ref="AR21:AV21"/>
     <mergeCell ref="AR11:AV11"/>
@@ -24193,15 +23593,15 @@
     <mergeCell ref="AK22:AO22"/>
     <mergeCell ref="AR22:AV22"/>
     <mergeCell ref="AY22:BC22"/>
-    <mergeCell ref="AY48:BC48"/>
-    <mergeCell ref="AY47:BC47"/>
-    <mergeCell ref="BF48:BJ48"/>
-    <mergeCell ref="BF47:BJ47"/>
+    <mergeCell ref="AY43:BC43"/>
+    <mergeCell ref="AY42:BC42"/>
+    <mergeCell ref="BF43:BJ43"/>
+    <mergeCell ref="BF42:BJ42"/>
     <mergeCell ref="BF21:BJ21"/>
-    <mergeCell ref="AD48:AH48"/>
-    <mergeCell ref="AD47:AH47"/>
+    <mergeCell ref="AD43:AH43"/>
+    <mergeCell ref="AD42:AH42"/>
     <mergeCell ref="AD9:AH9"/>
-    <mergeCell ref="BM48:BQ48"/>
+    <mergeCell ref="BM43:BQ43"/>
     <mergeCell ref="BF22:BJ22"/>
     <mergeCell ref="BM22:BQ22"/>
     <mergeCell ref="AD33:AH33"/>
@@ -24210,13 +23610,13 @@
     <mergeCell ref="AY33:BC33"/>
     <mergeCell ref="BF33:BJ33"/>
     <mergeCell ref="BM33:BQ33"/>
-    <mergeCell ref="I47:M47"/>
-    <mergeCell ref="I48:M48"/>
+    <mergeCell ref="I42:M42"/>
+    <mergeCell ref="I43:M43"/>
     <mergeCell ref="P7:T7"/>
     <mergeCell ref="W7:AA7"/>
     <mergeCell ref="P9:T9"/>
-    <mergeCell ref="P48:T48"/>
-    <mergeCell ref="P47:T47"/>
+    <mergeCell ref="P43:T43"/>
+    <mergeCell ref="P42:T42"/>
     <mergeCell ref="P21:T21"/>
     <mergeCell ref="P11:T11"/>
     <mergeCell ref="P10:T10"/>
@@ -24226,8 +23626,8 @@
     <mergeCell ref="I10:M10"/>
     <mergeCell ref="I11:M11"/>
     <mergeCell ref="I21:M21"/>
-    <mergeCell ref="W48:AA48"/>
-    <mergeCell ref="W47:AA47"/>
+    <mergeCell ref="W43:AA43"/>
+    <mergeCell ref="W42:AA42"/>
     <mergeCell ref="I7:M7"/>
     <mergeCell ref="I33:M33"/>
     <mergeCell ref="P33:T33"/>
@@ -24272,13 +23672,13 @@
     <mergeCell ref="BM10:BQ10"/>
     <mergeCell ref="BM9:BQ9"/>
     <mergeCell ref="BM7:BQ7"/>
-    <mergeCell ref="BT47:BX47"/>
+    <mergeCell ref="BT42:BX42"/>
     <mergeCell ref="BT21:BX21"/>
     <mergeCell ref="BT11:BX11"/>
     <mergeCell ref="BT10:BX10"/>
     <mergeCell ref="BT9:BX9"/>
     <mergeCell ref="BT7:BX7"/>
-    <mergeCell ref="BM47:BQ47"/>
+    <mergeCell ref="BM42:BQ42"/>
     <mergeCell ref="BT32:BX32"/>
     <mergeCell ref="BT22:BX22"/>
     <mergeCell ref="BT33:BX33"/>
@@ -24286,9 +23686,9 @@
     <mergeCell ref="CH10:CL10"/>
     <mergeCell ref="CH9:CL9"/>
     <mergeCell ref="CH7:CL7"/>
-    <mergeCell ref="CH48:CL48"/>
-    <mergeCell ref="CA48:CE48"/>
-    <mergeCell ref="CA47:CE47"/>
+    <mergeCell ref="CH43:CL43"/>
+    <mergeCell ref="CA43:CE43"/>
+    <mergeCell ref="CA42:CE42"/>
     <mergeCell ref="CA21:CE21"/>
     <mergeCell ref="CA11:CE11"/>
     <mergeCell ref="CA32:CE32"/>
@@ -24297,11 +23697,11 @@
     <mergeCell ref="CH22:CL22"/>
     <mergeCell ref="CA33:CE33"/>
     <mergeCell ref="CH33:CL33"/>
-    <mergeCell ref="CH47:CL47"/>
+    <mergeCell ref="CH42:CL42"/>
     <mergeCell ref="CH21:CL21"/>
     <mergeCell ref="CH11:CL11"/>
-    <mergeCell ref="CV48:CZ48"/>
-    <mergeCell ref="CV47:CZ47"/>
+    <mergeCell ref="CV43:CZ43"/>
+    <mergeCell ref="CV42:CZ42"/>
     <mergeCell ref="CO32:CS32"/>
     <mergeCell ref="CV32:CZ32"/>
     <mergeCell ref="CA10:CE10"/>
@@ -24320,8 +23720,8 @@
     <mergeCell ref="DC10:DG10"/>
     <mergeCell ref="DC9:DG9"/>
     <mergeCell ref="DC7:DG7"/>
-    <mergeCell ref="CO48:CS48"/>
-    <mergeCell ref="CO47:CS47"/>
+    <mergeCell ref="CO43:CS43"/>
+    <mergeCell ref="CO42:CS42"/>
     <mergeCell ref="CO21:CS21"/>
     <mergeCell ref="CO11:CS11"/>
     <mergeCell ref="CO7:CS7"/>
@@ -24330,8 +23730,8 @@
     <mergeCell ref="DQ10:DU10"/>
     <mergeCell ref="DQ9:DU9"/>
     <mergeCell ref="DQ7:DU7"/>
-    <mergeCell ref="DJ48:DN48"/>
-    <mergeCell ref="DJ47:DN47"/>
+    <mergeCell ref="DJ43:DN43"/>
+    <mergeCell ref="DJ42:DN42"/>
     <mergeCell ref="DJ21:DN21"/>
     <mergeCell ref="DJ11:DN11"/>
     <mergeCell ref="DJ10:DN10"/>
@@ -24341,18 +23741,18 @@
     <mergeCell ref="DQ22:DU22"/>
     <mergeCell ref="DJ33:DN33"/>
     <mergeCell ref="DQ33:DU33"/>
-    <mergeCell ref="DX48:EB48"/>
-    <mergeCell ref="DX47:EB47"/>
+    <mergeCell ref="DX43:EB43"/>
+    <mergeCell ref="DX42:EB42"/>
     <mergeCell ref="DX21:EB21"/>
     <mergeCell ref="DX11:EB11"/>
-    <mergeCell ref="DC47:DG47"/>
+    <mergeCell ref="DC42:DG42"/>
     <mergeCell ref="DC21:DG21"/>
     <mergeCell ref="DC11:DG11"/>
-    <mergeCell ref="DC48:DG48"/>
-    <mergeCell ref="DQ47:DU47"/>
+    <mergeCell ref="DC43:DG43"/>
+    <mergeCell ref="DQ42:DU42"/>
     <mergeCell ref="DQ21:DU21"/>
     <mergeCell ref="DQ11:DU11"/>
-    <mergeCell ref="DQ48:DU48"/>
+    <mergeCell ref="DQ43:DU43"/>
     <mergeCell ref="DX32:EB32"/>
     <mergeCell ref="DC32:DG32"/>
     <mergeCell ref="DJ32:DN32"/>
@@ -24365,8 +23765,8 @@
     <mergeCell ref="EE10:EI10"/>
     <mergeCell ref="EE11:EI11"/>
     <mergeCell ref="EE21:EI21"/>
-    <mergeCell ref="EE47:EI47"/>
-    <mergeCell ref="EE48:EI48"/>
+    <mergeCell ref="EE42:EI42"/>
+    <mergeCell ref="EE43:EI43"/>
     <mergeCell ref="EE32:EI32"/>
     <mergeCell ref="EL32:EP32"/>
     <mergeCell ref="EL33:EP33"/>
@@ -24374,8 +23774,8 @@
     <mergeCell ref="EL10:EP10"/>
     <mergeCell ref="EL11:EP11"/>
     <mergeCell ref="EL21:EP21"/>
-    <mergeCell ref="EL47:EP47"/>
-    <mergeCell ref="EL48:EP48"/>
+    <mergeCell ref="EL42:EP42"/>
+    <mergeCell ref="EL43:EP43"/>
     <mergeCell ref="EE22:EI22"/>
     <mergeCell ref="EL22:EP22"/>
     <mergeCell ref="EE33:EI33"/>
@@ -24383,13 +23783,13 @@
     <mergeCell ref="ES10:EW10"/>
     <mergeCell ref="ES11:EW11"/>
     <mergeCell ref="ES21:EW21"/>
-    <mergeCell ref="ES47:EW47"/>
-    <mergeCell ref="ES48:EW48"/>
+    <mergeCell ref="ES42:EW42"/>
+    <mergeCell ref="ES43:EW43"/>
     <mergeCell ref="ES32:EW32"/>
     <mergeCell ref="ES22:EW22"/>
     <mergeCell ref="ES33:EW33"/>
   </mergeCells>
-  <conditionalFormatting sqref="D8:D107">
+  <conditionalFormatting sqref="D8:D104">
     <cfRule type="dataBar" priority="100">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -24403,7 +23803,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I9:AO9 BM9:CS9 DX9:EB9 EE9:EI9 I47:AO47 BM47:CS47 DX47:EB47 EE47:EI47">
+  <conditionalFormatting sqref="I9:AO9 BM9:CS9 DX9:EB9 EE9:EI9 I42:AO42 BM42:CS42 DX42:EB42 EE42:EI42">
     <cfRule type="expression" dxfId="6" priority="32">
       <formula>AND(fin_tâche&gt;=I$6,début_tâche&lt;J$6)</formula>
     </cfRule>
@@ -24413,22 +23813,22 @@
       <formula>AND(fin_tâche&gt;=I$6,début_tâche&lt;J$6)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I10:EW46">
+  <conditionalFormatting sqref="I10:EW41">
     <cfRule type="expression" dxfId="4" priority="12" stopIfTrue="1">
       <formula>AND(fin_tâche&gt;=I$6,début_tâche&lt;J$6)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I47:EW47">
+  <conditionalFormatting sqref="I42:EW42">
     <cfRule type="expression" dxfId="3" priority="5" stopIfTrue="1">
       <formula>AND(fin_tâche&gt;=I$6,début_tâche&lt;J$6)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I48:EW64 I65:BQ69 BT65:EW69 I70:EW105">
+  <conditionalFormatting sqref="I43:EW59 I60:BQ66 BT60:EW66 I67:EW102">
     <cfRule type="expression" dxfId="2" priority="6" stopIfTrue="1">
       <formula>AND(fin_tâche&gt;=I$6,début_tâche&lt;J$6)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="EL9:EP9 EL47:EP47 ES47:EW47">
+  <conditionalFormatting sqref="EL9:EP9 EL42:EP42 ES42:EW42">
     <cfRule type="expression" dxfId="1" priority="20" stopIfTrue="1">
       <formula>AND(fin_tâche&gt;=EL$6,début_tâche&lt;EM$6)</formula>
     </cfRule>
@@ -24445,12 +23845,12 @@
   </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.35" right="0.35" top="0.35" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="17" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="22" orientation="landscape" r:id="rId1"/>
   <headerFooter differentFirst="1" scaleWithDoc="0">
     <oddFooter>Page &amp;P of &amp;N</oddFooter>
   </headerFooter>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="106" max="16383" man="1"/>
+    <brk id="103" max="16383" man="1"/>
   </rowBreaks>
   <colBreaks count="1" manualBreakCount="1">
     <brk id="2" max="1048575" man="1"/>
@@ -24471,7 +23871,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>D8:D107</xm:sqref>
+          <xm:sqref>D8:D104</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
